--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -475,10 +475,10 @@
         <v>entry fragger|star player</v>
       </c>
       <c r="D2">
-        <v>56666.666666666664</v>
+        <v>61906.666666666664</v>
       </c>
       <c r="E2">
-        <v>56666.666666666664</v>
+        <v>61906.666666666664</v>
       </c>
       <c r="F2">
         <v>11</v>
@@ -487,7 +487,7 @@
         <v>Lux Tenebris</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -670,10 +670,10 @@
         <v>igl|awper</v>
       </c>
       <c r="D5">
-        <v>47142.857142857145</v>
+        <v>50954.28571428572</v>
       </c>
       <c r="E5">
-        <v>47142.857142857145</v>
+        <v>50954.28571428572</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -685,13 +685,13 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -7625,10 +7625,10 @@
         <v>anchor</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F112">
         <v>5</v>
@@ -7690,10 +7690,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F113">
         <v>5</v>
@@ -7755,10 +7755,10 @@
         <v>igl</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F114">
         <v>5</v>
@@ -7820,10 +7820,10 @@
         <v>awper</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F115">
         <v>5</v>
@@ -7885,10 +7885,10 @@
         <v>star player</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F116">
         <v>5</v>
@@ -8600,10 +8600,10 @@
         <v>igl</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F127">
         <v>5</v>
@@ -8665,10 +8665,10 @@
         <v>awper</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F128">
         <v>5</v>
@@ -8730,10 +8730,10 @@
         <v>anchor</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F129">
         <v>5</v>
@@ -8795,10 +8795,10 @@
         <v>star player</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F130">
         <v>5</v>
@@ -8860,10 +8860,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F131">
         <v>5</v>
@@ -15100,10 +15100,10 @@
         <v>rifler</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F227">
         <v>5</v>
@@ -15165,10 +15165,10 @@
         <v>awper</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F228">
         <v>5</v>
@@ -15230,10 +15230,10 @@
         <v>anchor</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E229">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F229">
         <v>5</v>
@@ -15295,10 +15295,10 @@
         <v>rifler</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F230">
         <v>5</v>
@@ -15360,10 +15360,10 @@
         <v>igl</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F231">
         <v>5</v>
@@ -17050,10 +17050,10 @@
         <v>igl</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F257">
         <v>5</v>
@@ -17115,10 +17115,10 @@
         <v>awper</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F258">
         <v>5</v>
@@ -17180,10 +17180,10 @@
         <v>star player</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F259">
         <v>5</v>
@@ -17245,10 +17245,10 @@
         <v>anchor</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E260">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F260">
         <v>5</v>
@@ -17310,10 +17310,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D261">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E261">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F261">
         <v>5</v>
@@ -18350,10 +18350,10 @@
         <v>awper</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E277">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F277">
         <v>5</v>
@@ -18415,10 +18415,10 @@
         <v>igl</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E278">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F278">
         <v>5</v>
@@ -18480,10 +18480,10 @@
         <v>star player</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E279">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F279">
         <v>5</v>
@@ -18545,10 +18545,10 @@
         <v>rifler</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E280">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F280">
         <v>5</v>
@@ -18610,10 +18610,10 @@
         <v>anchor</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E281">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F281">
         <v>5</v>
@@ -22250,10 +22250,10 @@
         <v>igl</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E337">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F337">
         <v>5</v>
@@ -22315,10 +22315,10 @@
         <v>rifler</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E338">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F338">
         <v>5</v>
@@ -22380,10 +22380,10 @@
         <v>anchor</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E339">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F339">
         <v>5</v>
@@ -22445,10 +22445,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E340">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F340">
         <v>5</v>
@@ -22510,10 +22510,10 @@
         <v>awper</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E341">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F341">
         <v>5</v>
@@ -23550,10 +23550,10 @@
         <v>awper</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="F357">
         <v>5</v>
@@ -23568,7 +23568,7 @@
         <v>0</v>
       </c>
       <c r="J357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357">
         <v>0</v>
@@ -23615,10 +23615,10 @@
         <v>igl</v>
       </c>
       <c r="D358">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E358">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F358">
         <v>5</v>
@@ -23680,10 +23680,10 @@
         <v>rifler</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F359">
         <v>5</v>
@@ -23745,10 +23745,10 @@
         <v>anchor</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E360">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F360">
         <v>5</v>
@@ -23810,10 +23810,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D361">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E361">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F361">
         <v>5</v>
@@ -56505,10 +56505,10 @@
         <v>anchor</v>
       </c>
       <c r="D864">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="E864">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="F864">
         <v>13</v>
@@ -56523,10 +56523,10 @@
         <v>0</v>
       </c>
       <c r="J864">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K864">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L864">
         <v>0</v>
@@ -56765,10 +56765,10 @@
         <v>anchor</v>
       </c>
       <c r="D868">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="E868">
-        <v>0</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="F868">
         <v>7</v>
@@ -56783,10 +56783,10 @@
         <v>0</v>
       </c>
       <c r="J868">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K868">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L868">
         <v>0</v>
@@ -56895,10 +56895,10 @@
         <v>rifler</v>
       </c>
       <c r="D870">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E870">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F870">
         <v>12</v>
@@ -56916,7 +56916,7 @@
         <v>0</v>
       </c>
       <c r="K870">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L870">
         <v>0</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -38500,10 +38500,10 @@
         <v>rifler</v>
       </c>
       <c r="D587">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E587">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F587">
         <v>5</v>
@@ -38521,7 +38521,7 @@
         <v>0</v>
       </c>
       <c r="K587">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L587">
         <v>0</v>
@@ -38565,10 +38565,10 @@
         <v>anchor</v>
       </c>
       <c r="D588">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E588">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F588">
         <v>5</v>
@@ -38586,7 +38586,7 @@
         <v>0</v>
       </c>
       <c r="K588">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L588">
         <v>0</v>
@@ -38630,10 +38630,10 @@
         <v>igl</v>
       </c>
       <c r="D589">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E589">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F589">
         <v>5</v>
@@ -38651,7 +38651,7 @@
         <v>0</v>
       </c>
       <c r="K589">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L589">
         <v>0</v>
@@ -38695,10 +38695,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D590">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E590">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F590">
         <v>5</v>
@@ -38716,7 +38716,7 @@
         <v>0</v>
       </c>
       <c r="K590">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L590">
         <v>0</v>
@@ -38760,10 +38760,10 @@
         <v>awper</v>
       </c>
       <c r="D591">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E591">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F591">
         <v>5</v>
@@ -38781,7 +38781,7 @@
         <v>0</v>
       </c>
       <c r="K591">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L591">
         <v>0</v>
@@ -39475,10 +39475,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D602">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E602">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F602">
         <v>5</v>
@@ -39540,10 +39540,10 @@
         <v>anchor</v>
       </c>
       <c r="D603">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E603">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F603">
         <v>5</v>
@@ -39605,10 +39605,10 @@
         <v>awper</v>
       </c>
       <c r="D604">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E604">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F604">
         <v>5</v>
@@ -39670,10 +39670,10 @@
         <v>igl</v>
       </c>
       <c r="D605">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E605">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F605">
         <v>5</v>
@@ -39735,10 +39735,10 @@
         <v>rifler</v>
       </c>
       <c r="D606">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E606">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F606">
         <v>5</v>
@@ -41425,10 +41425,10 @@
         <v>rifler</v>
       </c>
       <c r="D632">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E632">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F632">
         <v>5</v>
@@ -41490,10 +41490,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D633">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E633">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F633">
         <v>5</v>
@@ -41555,10 +41555,10 @@
         <v>anchor</v>
       </c>
       <c r="D634">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E634">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F634">
         <v>5</v>
@@ -41620,10 +41620,10 @@
         <v>awper</v>
       </c>
       <c r="D635">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E635">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F635">
         <v>5</v>
@@ -41685,10 +41685,10 @@
         <v>igl</v>
       </c>
       <c r="D636">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E636">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F636">
         <v>5</v>
@@ -43375,10 +43375,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D662">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E662">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F662">
         <v>5</v>
@@ -43440,10 +43440,10 @@
         <v>anchor</v>
       </c>
       <c r="D663">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E663">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F663">
         <v>5</v>
@@ -43505,10 +43505,10 @@
         <v>igl</v>
       </c>
       <c r="D664">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E664">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F664">
         <v>5</v>
@@ -43570,10 +43570,10 @@
         <v>awper</v>
       </c>
       <c r="D665">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E665">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F665">
         <v>5</v>
@@ -43635,10 +43635,10 @@
         <v>rifler</v>
       </c>
       <c r="D666">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E666">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F666">
         <v>5</v>
@@ -43700,10 +43700,10 @@
         <v>anchor</v>
       </c>
       <c r="D667">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E667">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F667">
         <v>5</v>
@@ -43765,10 +43765,10 @@
         <v>awper</v>
       </c>
       <c r="D668">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E668">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F668">
         <v>5</v>
@@ -43830,10 +43830,10 @@
         <v>rifler</v>
       </c>
       <c r="D669">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E669">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F669">
         <v>5</v>
@@ -43895,10 +43895,10 @@
         <v>igl</v>
       </c>
       <c r="D670">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E670">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F670">
         <v>5</v>
@@ -43960,10 +43960,10 @@
         <v>awper</v>
       </c>
       <c r="D671">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E671">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F671">
         <v>5</v>
@@ -49225,10 +49225,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D752">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E752">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F752">
         <v>5</v>
@@ -49290,10 +49290,10 @@
         <v>awper</v>
       </c>
       <c r="D753">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E753">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F753">
         <v>5</v>
@@ -49355,10 +49355,10 @@
         <v>igl</v>
       </c>
       <c r="D754">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E754">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F754">
         <v>5</v>
@@ -49420,10 +49420,10 @@
         <v>rifler</v>
       </c>
       <c r="D755">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E755">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F755">
         <v>5</v>
@@ -49485,10 +49485,10 @@
         <v>anchor</v>
       </c>
       <c r="D756">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E756">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F756">
         <v>5</v>
@@ -53125,10 +53125,10 @@
         <v>rifler</v>
       </c>
       <c r="D812">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E812">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F812">
         <v>5</v>
@@ -53190,10 +53190,10 @@
         <v>awper</v>
       </c>
       <c r="D813">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E813">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F813">
         <v>5</v>
@@ -53255,10 +53255,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D814">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E814">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F814">
         <v>5</v>
@@ -53320,10 +53320,10 @@
         <v>igl</v>
       </c>
       <c r="D815">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E815">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F815">
         <v>5</v>
@@ -53385,10 +53385,10 @@
         <v>anchor</v>
       </c>
       <c r="D816">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E816">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F816">
         <v>5</v>
@@ -53450,10 +53450,10 @@
         <v>igl</v>
       </c>
       <c r="D817">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E817">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F817">
         <v>5</v>
@@ -53515,10 +53515,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D818">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E818">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F818">
         <v>5</v>
@@ -53580,10 +53580,10 @@
         <v>awper</v>
       </c>
       <c r="D819">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E819">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F819">
         <v>5</v>
@@ -53645,10 +53645,10 @@
         <v>rifler</v>
       </c>
       <c r="D820">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E820">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F820">
         <v>5</v>
@@ -53710,10 +53710,10 @@
         <v>anchor</v>
       </c>
       <c r="D821">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E821">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F821">
         <v>5</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -38565,10 +38565,10 @@
         <v>anchor</v>
       </c>
       <c r="D588">
-        <v>240</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="E588">
-        <v>240</v>
+        <v>2382.8571428571427</v>
       </c>
       <c r="F588">
         <v>5</v>
@@ -38583,7 +38583,7 @@
         <v>0</v>
       </c>
       <c r="J588">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K588">
         <v>1</v>
@@ -39735,10 +39735,10 @@
         <v>rifler</v>
       </c>
       <c r="D606">
-        <v>120</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="E606">
-        <v>120</v>
+        <v>2262.8571428571427</v>
       </c>
       <c r="F606">
         <v>5</v>
@@ -39753,7 +39753,7 @@
         <v>0</v>
       </c>
       <c r="J606">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K606">
         <v>0</v>
@@ -53125,10 +53125,10 @@
         <v>rifler</v>
       </c>
       <c r="D812">
-        <v>160</v>
+        <v>2302.8571428571427</v>
       </c>
       <c r="E812">
-        <v>160</v>
+        <v>2302.8571428571427</v>
       </c>
       <c r="F812">
         <v>5</v>
@@ -53143,7 +53143,7 @@
         <v>0</v>
       </c>
       <c r="J812">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K812">
         <v>0</v>
@@ -53190,10 +53190,10 @@
         <v>awper</v>
       </c>
       <c r="D813">
-        <v>160</v>
+        <v>3731.428571428571</v>
       </c>
       <c r="E813">
-        <v>160</v>
+        <v>3731.428571428571</v>
       </c>
       <c r="F813">
         <v>5</v>
@@ -53205,7 +53205,7 @@
         <v>0</v>
       </c>
       <c r="I813">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J813">
         <v>0</v>
@@ -53255,10 +53255,10 @@
         <v>entry fragger</v>
       </c>
       <c r="D814">
-        <v>160</v>
+        <v>5160</v>
       </c>
       <c r="E814">
-        <v>160</v>
+        <v>5160</v>
       </c>
       <c r="F814">
         <v>5</v>
@@ -53267,7 +53267,7 @@
         <v>kONO</v>
       </c>
       <c r="H814">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I814">
         <v>0</v>

--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -481,7 +481,7 @@
         <v>61906.666666666664</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="str">
         <v>Lux Tenebris</v>
@@ -546,7 +546,7 @@
         <v>40000</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
         <v>Iluminar</v>
@@ -611,7 +611,7 @@
         <v>40000</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="str">
         <v>Iluminar</v>
@@ -676,7 +676,7 @@
         <v>50954.28571428572</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="str">
         <v>Lux Tenebris</v>
@@ -741,7 +741,7 @@
         <v>40000</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="str">
         <v>Iluminar</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="str">
         <v>Wizards</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="str">
         <v>Wizards</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
         <v>Wizards</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="str">
         <v>Wizards</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
         <v>Wizards</v>
@@ -1131,7 +1131,7 @@
         <v>56</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="str">
         <v>Legacy</v>
@@ -1196,7 +1196,7 @@
         <v>56</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="str">
         <v>Legacy</v>
@@ -1261,7 +1261,7 @@
         <v>56</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
         <v>Legacy</v>
@@ -1326,7 +1326,7 @@
         <v>56</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
         <v>Legacy</v>
@@ -1391,7 +1391,7 @@
         <v>56</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="str">
         <v>Legacy</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" t="str">
         <v>Underground</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="str">
         <v>Underground</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="str">
         <v>Underground</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="str">
         <v>Underground</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="str">
         <v>Underground</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="str">
         <v>Bad News Eagles</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="str">
         <v>Bad News Eagles</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="str">
         <v>Bad News Eagles</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
         <v>Bad News Eagles</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="str">
         <v>Bad News Eagles</v>
@@ -2106,7 +2106,7 @@
         <v>25504.761904761905</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="str">
         <v>Vitality</v>
@@ -2171,7 +2171,7 @@
         <v>13600</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="str">
         <v>Vitality</v>
@@ -2236,7 +2236,7 @@
         <v>20742.85714285714</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="str">
         <v>Vitality</v>
@@ -2301,7 +2301,7 @@
         <v>13600</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="str">
         <v>Vitality</v>
@@ -2366,7 +2366,7 @@
         <v>13600</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="str">
         <v>Vitality</v>
@@ -2431,7 +2431,7 @@
         <v>1200</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="str">
         <v>Spirit</v>
@@ -2496,7 +2496,7 @@
         <v>1200</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="str">
         <v>Spirit</v>
@@ -2561,7 +2561,7 @@
         <v>1200</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="str">
         <v>Spirit</v>
@@ -2626,7 +2626,7 @@
         <v>1200</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="str">
         <v>Spirit</v>
@@ -2691,7 +2691,7 @@
         <v>1200</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" t="str">
         <v>Spirit</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" t="str">
         <v>FaZe</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
         <v>FaZe</v>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="str">
         <v>FaZe</v>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G40" t="str">
         <v>FaZe</v>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" t="str">
         <v>FaZe</v>
@@ -3081,7 +3081,7 @@
         <v>1200</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="str">
         <v>Cloud9</v>
@@ -3146,7 +3146,7 @@
         <v>1200</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="str">
         <v>Cloud9</v>
@@ -3211,7 +3211,7 @@
         <v>1200</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" t="str">
         <v>Cloud9</v>
@@ -3276,7 +3276,7 @@
         <v>1200</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G45" t="str">
         <v>Cloud9</v>
@@ -3341,7 +3341,7 @@
         <v>1200</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G46" t="str">
         <v>Cloud9</v>
@@ -3406,7 +3406,7 @@
         <v>15142.857142857141</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G47" t="str">
         <v>Falcons</v>
@@ -3471,7 +3471,7 @@
         <v>8000</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G48" t="str">
         <v>Falcons</v>
@@ -3536,7 +3536,7 @@
         <v>8000</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G49" t="str">
         <v>Falcons</v>
@@ -3601,7 +3601,7 @@
         <v>8000</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" t="str">
         <v>Falcons</v>
@@ -3666,7 +3666,7 @@
         <v>8000</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" t="str">
         <v>Falcons</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" t="str">
         <v>Aurora</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G53" t="str">
         <v>Aurora</v>
@@ -3861,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="str">
         <v>Aurora</v>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="str">
         <v>Aurora</v>
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="str">
         <v>Aurora</v>
@@ -4056,7 +4056,7 @@
         <v>2000</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57" t="str">
         <v>Elevate</v>
@@ -4121,7 +4121,7 @@
         <v>2000</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="str">
         <v>Elevate</v>
@@ -4186,7 +4186,7 @@
         <v>2000</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" t="str">
         <v>Elevate</v>
@@ -4251,7 +4251,7 @@
         <v>2000</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" t="str">
         <v>Elevate</v>
@@ -4316,7 +4316,7 @@
         <v>2000</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61" t="str">
         <v>Elevate</v>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G62" t="str">
         <v>Orbit</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" t="str">
         <v>Orbit</v>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" t="str">
         <v>Orbit</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
         <v>Orbit</v>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G66" t="str">
         <v>Orbit</v>
@@ -4706,7 +4706,7 @@
         <v>800</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" t="str">
         <v>Bounty Hunters</v>
@@ -4771,7 +4771,7 @@
         <v>800</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" t="str">
         <v>Bounty Hunters</v>
@@ -4836,7 +4836,7 @@
         <v>800</v>
       </c>
       <c r="F69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G69" t="str">
         <v>Bounty Hunters</v>
@@ -4901,7 +4901,7 @@
         <v>800</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70" t="str">
         <v>Bounty Hunters</v>
@@ -4966,7 +4966,7 @@
         <v>800</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" t="str">
         <v>Bounty Hunters</v>
@@ -5031,7 +5031,7 @@
         <v>4800</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" t="str">
         <v>Liquid</v>
@@ -5096,7 +5096,7 @@
         <v>4800</v>
       </c>
       <c r="F73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" t="str">
         <v>Liquid</v>
@@ -5161,7 +5161,7 @@
         <v>4800</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74" t="str">
         <v>Liquid</v>
@@ -5226,7 +5226,7 @@
         <v>4800</v>
       </c>
       <c r="F75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" t="str">
         <v>Liquid</v>
@@ -5291,7 +5291,7 @@
         <v>4800</v>
       </c>
       <c r="F76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" t="str">
         <v>Liquid</v>
@@ -5356,7 +5356,7 @@
         <v>2000</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" t="str">
         <v>Titan</v>
@@ -5421,7 +5421,7 @@
         <v>2000</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" t="str">
         <v>Titan</v>
@@ -5486,7 +5486,7 @@
         <v>2000</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79" t="str">
         <v>Titan</v>
@@ -5551,7 +5551,7 @@
         <v>2000</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" t="str">
         <v>Titan</v>
@@ -5616,7 +5616,7 @@
         <v>2000</v>
       </c>
       <c r="F81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" t="str">
         <v>Titan</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" t="str">
         <v>Case</v>
@@ -5746,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" t="str">
         <v>Case</v>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" t="str">
         <v>Case</v>
@@ -5876,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G85" t="str">
         <v>Case</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G86" t="str">
         <v>Case</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G87" t="str">
         <v>MIBR</v>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88" t="str">
         <v>MIBR</v>
@@ -6136,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G89" t="str">
         <v>MIBR</v>
@@ -6201,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G90" t="str">
         <v>MIBR</v>
@@ -6266,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G91" t="str">
         <v>MIBR</v>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" t="str">
         <v>Complexity</v>
@@ -6396,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G93" t="str">
         <v>Complexity</v>
@@ -6461,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" t="str">
         <v>Complexity</v>
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G95" t="str">
         <v>Complexity</v>
@@ -6591,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G96" t="str">
         <v>Complexity</v>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" t="str">
         <v>Kappa Bar</v>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G98" t="str">
         <v>Kappa Bar</v>
@@ -6786,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="F99">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G99" t="str">
         <v>Iluminar</v>
@@ -6851,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="F100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G100" t="str">
         <v>Kappa Bar</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G101" t="str">
         <v>Kappa Bar</v>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G102" t="str">
         <v>GODSENT</v>
@@ -7046,7 +7046,7 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G103" t="str">
         <v>GODSENT</v>
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G104" t="str">
         <v>GODSENT</v>
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G105" t="str">
         <v>GODSENT</v>
@@ -7241,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G106" t="str">
         <v>GODSENT</v>
@@ -7306,7 +7306,7 @@
         <v>0</v>
       </c>
       <c r="F107">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G107" t="str">
         <v>Iluminar</v>
@@ -7371,7 +7371,7 @@
         <v>56</v>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G108" t="str">
         <v>Mythic</v>
@@ -7436,7 +7436,7 @@
         <v>56</v>
       </c>
       <c r="F109">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G109" t="str">
         <v>Mythic</v>
@@ -7501,7 +7501,7 @@
         <v>56</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G110" t="str">
         <v>Mythic</v>
@@ -7566,7 +7566,7 @@
         <v>56</v>
       </c>
       <c r="F111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G111" t="str">
         <v>Mythic</v>
@@ -7631,7 +7631,7 @@
         <v>56</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G112" t="str">
         <v>Enemy</v>
@@ -7696,7 +7696,7 @@
         <v>56</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G113" t="str">
         <v>Enemy</v>
@@ -7761,7 +7761,7 @@
         <v>56</v>
       </c>
       <c r="F114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G114" t="str">
         <v>Enemy</v>
@@ -7826,7 +7826,7 @@
         <v>56</v>
       </c>
       <c r="F115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G115" t="str">
         <v>Enemy</v>
@@ -7891,7 +7891,7 @@
         <v>56</v>
       </c>
       <c r="F116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G116" t="str">
         <v>Enemy</v>
@@ -7956,7 +7956,7 @@
         <v>240</v>
       </c>
       <c r="F117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G117" t="str">
         <v>FURIA</v>
@@ -8021,7 +8021,7 @@
         <v>2382.8571428571427</v>
       </c>
       <c r="F118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G118" t="str">
         <v>FURIA</v>
@@ -8086,7 +8086,7 @@
         <v>240</v>
       </c>
       <c r="F119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G119" t="str">
         <v>FURIA</v>
@@ -8151,7 +8151,7 @@
         <v>3811.428571428571</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G120" t="str">
         <v>FURIA</v>
@@ -8216,7 +8216,7 @@
         <v>5240</v>
       </c>
       <c r="F121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G121" t="str">
         <v>FURIA</v>
@@ -8281,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G122" t="str">
         <v>KRU</v>
@@ -8346,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G123" t="str">
         <v>KRU</v>
@@ -8411,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G124" t="str">
         <v>KRU</v>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G125" t="str">
         <v>KRU</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G126" t="str">
         <v>KRU</v>
@@ -8606,7 +8606,7 @@
         <v>160</v>
       </c>
       <c r="F127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G127" t="str">
         <v>Imperial</v>
@@ -8671,7 +8671,7 @@
         <v>160</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G128" t="str">
         <v>Imperial</v>
@@ -8736,7 +8736,7 @@
         <v>160</v>
       </c>
       <c r="F129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G129" t="str">
         <v>Imperial</v>
@@ -8801,7 +8801,7 @@
         <v>160</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G130" t="str">
         <v>Imperial</v>
@@ -8866,7 +8866,7 @@
         <v>160</v>
       </c>
       <c r="F131">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G131" t="str">
         <v>Imperial</v>
@@ -8931,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="F132">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G132" t="str">
         <v>9z</v>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G133" t="str">
         <v>9z</v>
@@ -9061,7 +9061,7 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G134" t="str">
         <v>9z</v>
@@ -9126,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G135" t="str">
         <v>9z</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="F136">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G136" t="str">
         <v>9z</v>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="F137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G137" t="str">
         <v>paiN</v>
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="F138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G138" t="str">
         <v>paiN</v>
@@ -9386,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="F139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G139" t="str">
         <v>paiN</v>
@@ -9451,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="F140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G140" t="str">
         <v>paiN</v>
@@ -9516,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G141" t="str">
         <v>paiN</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G142" t="str">
         <v>The Huns</v>
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G143" t="str">
         <v>The Huns</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="F144">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G144" t="str">
         <v>The Huns</v>
@@ -9776,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="F145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G145" t="str">
         <v>The Huns</v>
@@ -9841,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="F146">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G146" t="str">
         <v>The Huns</v>
@@ -9906,7 +9906,7 @@
         <v>0</v>
       </c>
       <c r="F147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G147" t="str">
         <v>Vexed</v>
@@ -9971,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G148" t="str">
         <v>Vexed</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G149" t="str">
         <v>Vexed</v>
@@ -10101,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G150" t="str">
         <v>Vexed</v>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G151" t="str">
         <v>Vexed</v>
@@ -10231,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="F152">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G152" t="str">
         <v>M80</v>
@@ -10296,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G153" t="str">
         <v>M80</v>
@@ -10361,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G154" t="str">
         <v>M80</v>
@@ -10426,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G155" t="str">
         <v>M80</v>
@@ -10491,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="F156">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G156" t="str">
         <v>M80</v>
@@ -10556,7 +10556,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G157" t="str">
         <v>IHC</v>
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G158" t="str">
         <v>IHC</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G159" t="str">
         <v>IHC</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="F160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G160" t="str">
         <v>IHC</v>
@@ -10816,7 +10816,7 @@
         <v>0</v>
       </c>
       <c r="F161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G161" t="str">
         <v>IHC</v>
@@ -10881,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G162" t="str">
         <v>SK</v>
@@ -10946,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="F163">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G163" t="str">
         <v>SK</v>
@@ -11011,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="F164">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G164" t="str">
         <v>SK</v>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G165" t="str">
         <v>SK</v>
@@ -11141,7 +11141,7 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G166" t="str">
         <v>SK</v>
@@ -11206,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G167" t="str">
         <v>Sharks</v>
@@ -11271,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="F168">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G168" t="str">
         <v>Sharks</v>
@@ -11336,7 +11336,7 @@
         <v>0</v>
       </c>
       <c r="F169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G169" t="str">
         <v>Sharks</v>
@@ -11401,7 +11401,7 @@
         <v>0</v>
       </c>
       <c r="F170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G170" t="str">
         <v>Sharks</v>
@@ -11466,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="F171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G171" t="str">
         <v>Sharks</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G172" t="str">
         <v>Luminosity</v>
@@ -11596,7 +11596,7 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G173" t="str">
         <v>Luminosity</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G174" t="str">
         <v>Luminosity</v>
@@ -11726,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G175" t="str">
         <v>Luminosity</v>
@@ -11791,7 +11791,7 @@
         <v>0</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G176" t="str">
         <v>Luminosity</v>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="F177">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G177" t="str">
         <v>RED Canids</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="F178">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G178" t="str">
         <v>RED Canids</v>
@@ -11986,7 +11986,7 @@
         <v>0</v>
       </c>
       <c r="F179">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G179" t="str">
         <v>RED Canids</v>
@@ -12051,7 +12051,7 @@
         <v>0</v>
       </c>
       <c r="F180">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G180" t="str">
         <v>RED Canids</v>
@@ -12116,7 +12116,7 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G181" t="str">
         <v>RED Canids</v>
@@ -12181,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G182" t="str">
         <v>ECSTATIC</v>
@@ -12246,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G183" t="str">
         <v>ECSTATIC</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G184" t="str">
         <v>ECSTATIC</v>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G185" t="str">
         <v>ECSTATIC</v>
@@ -12441,7 +12441,7 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G186" t="str">
         <v>ECSTATIC</v>
@@ -12506,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="F187">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G187" t="str">
         <v>devils.one</v>
@@ -12571,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="F188">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G188" t="str">
         <v>devils.one</v>
@@ -12636,7 +12636,7 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G189" t="str">
         <v>devils.one</v>
@@ -12701,7 +12701,7 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G190" t="str">
         <v>devils.one</v>
@@ -12766,7 +12766,7 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G191" t="str">
         <v>devils.one</v>
@@ -12831,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="F192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G192" t="str">
         <v>OG</v>
@@ -12896,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="F193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G193" t="str">
         <v>OG</v>
@@ -12961,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="F194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G194" t="str">
         <v>OG</v>
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G195" t="str">
         <v>OG</v>
@@ -13091,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="F196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G196" t="str">
         <v>OG</v>
@@ -13156,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G197" t="str">
         <v>Galorys</v>
@@ -13221,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G198" t="str">
         <v>Galorys</v>
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="F199">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G199" t="str">
         <v>Galorys</v>
@@ -13351,7 +13351,7 @@
         <v>0</v>
       </c>
       <c r="F200">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G200" t="str">
         <v>Galorys</v>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="F201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G201" t="str">
         <v>Galorys</v>
@@ -13481,7 +13481,7 @@
         <v>0</v>
       </c>
       <c r="F202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G202" t="str">
         <v>Limitless</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G203" t="str">
         <v>Limitless</v>
@@ -13611,7 +13611,7 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G204" t="str">
         <v>Limitless</v>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="F205">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G205" t="str">
         <v>Limitless</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G206" t="str">
         <v>Limitless</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="F207">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G207" t="str">
         <v>Ninjas in Pyjamas</v>
@@ -13871,7 +13871,7 @@
         <v>0</v>
       </c>
       <c r="F208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G208" t="str">
         <v>Ninjas in Pyjamas</v>
@@ -13936,7 +13936,7 @@
         <v>0</v>
       </c>
       <c r="F209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G209" t="str">
         <v>Ninjas in Pyjamas</v>
@@ -14001,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="F210">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G210" t="str">
         <v>Ninjas in Pyjamas</v>
@@ -14066,7 +14066,7 @@
         <v>0</v>
       </c>
       <c r="F211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G211" t="str">
         <v>Ninjas in Pyjamas</v>
@@ -14131,7 +14131,7 @@
         <v>3600</v>
       </c>
       <c r="F212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G212" t="str">
         <v>Copenhagen Flames</v>
@@ -14196,7 +14196,7 @@
         <v>3600</v>
       </c>
       <c r="F213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G213" t="str">
         <v>Copenhagen Flames</v>
@@ -14261,7 +14261,7 @@
         <v>3600</v>
       </c>
       <c r="F214">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G214" t="str">
         <v>Copenhagen Flames</v>
@@ -14326,7 +14326,7 @@
         <v>3600</v>
       </c>
       <c r="F215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G215" t="str">
         <v>Copenhagen Flames</v>
@@ -14391,7 +14391,7 @@
         <v>3600</v>
       </c>
       <c r="F216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G216" t="str">
         <v>Copenhagen Flames</v>
@@ -14456,7 +14456,7 @@
         <v>1200</v>
       </c>
       <c r="F217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G217" t="str">
         <v>Heroic</v>
@@ -14521,7 +14521,7 @@
         <v>1200</v>
       </c>
       <c r="F218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G218" t="str">
         <v>Heroic</v>
@@ -14586,7 +14586,7 @@
         <v>1200</v>
       </c>
       <c r="F219">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G219" t="str">
         <v>Heroic</v>
@@ -14651,7 +14651,7 @@
         <v>1200</v>
       </c>
       <c r="F220">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G220" t="str">
         <v>Heroic</v>
@@ -14716,7 +14716,7 @@
         <v>1200</v>
       </c>
       <c r="F221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G221" t="str">
         <v>Heroic</v>
@@ -14781,7 +14781,7 @@
         <v>0</v>
       </c>
       <c r="F222">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G222" t="str">
         <v>BIG</v>
@@ -14846,7 +14846,7 @@
         <v>0</v>
       </c>
       <c r="F223">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G223" t="str">
         <v>BIG</v>
@@ -14911,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="F224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G224" t="str">
         <v>BIG</v>
@@ -14976,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="F225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G225" t="str">
         <v>BIG</v>
@@ -15041,7 +15041,7 @@
         <v>0</v>
       </c>
       <c r="F226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G226" t="str">
         <v>BIG</v>
@@ -15106,7 +15106,7 @@
         <v>56</v>
       </c>
       <c r="F227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G227" t="str">
         <v>Envy</v>
@@ -15171,7 +15171,7 @@
         <v>56</v>
       </c>
       <c r="F228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G228" t="str">
         <v>Envy</v>
@@ -15236,7 +15236,7 @@
         <v>56</v>
       </c>
       <c r="F229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G229" t="str">
         <v>Envy</v>
@@ -15289,7 +15289,7 @@
         <v>PTC</v>
       </c>
       <c r="B230" t="str">
-        <v>Starter</v>
+        <v/>
       </c>
       <c r="C230" t="str">
         <v>rifler</v>
@@ -15301,10 +15301,10 @@
         <v>56</v>
       </c>
       <c r="F230">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G230" t="str">
-        <v>Envy</v>
+        <v>none</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -15343,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="T230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U230" t="str">
         <v/>
@@ -15366,7 +15366,7 @@
         <v>56</v>
       </c>
       <c r="F231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G231" t="str">
         <v>Envy</v>
@@ -15431,7 +15431,7 @@
         <v>0</v>
       </c>
       <c r="F232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G232" t="str">
         <v>Nexus</v>
@@ -15496,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="F233">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G233" t="str">
         <v>Nexus</v>
@@ -15561,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="F234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G234" t="str">
         <v>Nexus</v>
@@ -15626,7 +15626,7 @@
         <v>0</v>
       </c>
       <c r="F235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G235" t="str">
         <v>Nexus</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="F236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G236" t="str">
         <v>Nexus</v>
@@ -15756,7 +15756,7 @@
         <v>0</v>
       </c>
       <c r="F237">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G237" t="str">
         <v>FlyQuest</v>
@@ -15821,7 +15821,7 @@
         <v>0</v>
       </c>
       <c r="F238">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G238" t="str">
         <v>FlyQuest</v>
@@ -15886,7 +15886,7 @@
         <v>0</v>
       </c>
       <c r="F239">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G239" t="str">
         <v>FlyQuest</v>
@@ -15951,7 +15951,7 @@
         <v>0</v>
       </c>
       <c r="F240">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G240" t="str">
         <v>FlyQuest</v>
@@ -16016,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="F241">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G241" t="str">
         <v>FlyQuest</v>
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="F242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G242" t="str">
         <v>Wildcard</v>
@@ -16146,7 +16146,7 @@
         <v>0</v>
       </c>
       <c r="F243">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G243" t="str">
         <v>Wildcard</v>
@@ -16211,7 +16211,7 @@
         <v>0</v>
       </c>
       <c r="F244">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G244" t="str">
         <v>Wildcard</v>
@@ -16276,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="F245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G245" t="str">
         <v>Wildcard</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="F246">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G246" t="str">
         <v>Wildcard</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="F247">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G247" t="str">
         <v>Passion UA</v>
@@ -16471,7 +16471,7 @@
         <v>0</v>
       </c>
       <c r="F248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G248" t="str">
         <v>Passion UA</v>
@@ -16536,7 +16536,7 @@
         <v>0</v>
       </c>
       <c r="F249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G249" t="str">
         <v>Passion UA</v>
@@ -16601,7 +16601,7 @@
         <v>0</v>
       </c>
       <c r="F250">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G250" t="str">
         <v>Passion UA</v>
@@ -16666,7 +16666,7 @@
         <v>0</v>
       </c>
       <c r="F251">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G251" t="str">
         <v>Passion UA</v>
@@ -16731,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="F252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G252" t="str">
         <v>GamerLegion</v>
@@ -16796,7 +16796,7 @@
         <v>0</v>
       </c>
       <c r="F253">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G253" t="str">
         <v>GamerLegion</v>
@@ -16861,7 +16861,7 @@
         <v>0</v>
       </c>
       <c r="F254">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G254" t="str">
         <v>GamerLegion</v>
@@ -16926,7 +16926,7 @@
         <v>0</v>
       </c>
       <c r="F255">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G255" t="str">
         <v>GamerLegion</v>
@@ -16991,7 +16991,7 @@
         <v>0</v>
       </c>
       <c r="F256">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G256" t="str">
         <v>GamerLegion</v>
@@ -17056,7 +17056,7 @@
         <v>56</v>
       </c>
       <c r="F257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G257" t="str">
         <v>MOUZ</v>
@@ -17121,7 +17121,7 @@
         <v>56</v>
       </c>
       <c r="F258">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G258" t="str">
         <v>MOUZ</v>
@@ -17186,7 +17186,7 @@
         <v>56</v>
       </c>
       <c r="F259">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G259" t="str">
         <v>MOUZ</v>
@@ -17251,7 +17251,7 @@
         <v>56</v>
       </c>
       <c r="F260">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G260" t="str">
         <v>MOUZ</v>
@@ -17316,7 +17316,7 @@
         <v>56</v>
       </c>
       <c r="F261">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G261" t="str">
         <v>MOUZ</v>
@@ -17381,7 +17381,7 @@
         <v>800</v>
       </c>
       <c r="F262">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G262" t="str">
         <v>Rebels</v>
@@ -17446,7 +17446,7 @@
         <v>800</v>
       </c>
       <c r="F263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G263" t="str">
         <v>Rebels</v>
@@ -17511,7 +17511,7 @@
         <v>800</v>
       </c>
       <c r="F264">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G264" t="str">
         <v>Rebels</v>
@@ -17576,7 +17576,7 @@
         <v>800</v>
       </c>
       <c r="F265">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G265" t="str">
         <v>Rebels</v>
@@ -17641,7 +17641,7 @@
         <v>800</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G266" t="str">
         <v>Rebels</v>
@@ -17706,7 +17706,7 @@
         <v>0</v>
       </c>
       <c r="F267">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G267" t="str">
         <v>LDLC</v>
@@ -17771,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="F268">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G268" t="str">
         <v>LDLC</v>
@@ -17836,7 +17836,7 @@
         <v>0</v>
       </c>
       <c r="F269">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G269" t="str">
         <v>LDLC</v>
@@ -17901,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="F270">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G270" t="str">
         <v>LDLC</v>
@@ -17966,7 +17966,7 @@
         <v>0</v>
       </c>
       <c r="F271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G271" t="str">
         <v>LDLC</v>
@@ -18031,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="F272">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G272" t="str">
         <v>ARCRED</v>
@@ -18096,7 +18096,7 @@
         <v>0</v>
       </c>
       <c r="F273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G273" t="str">
         <v>ARCRED</v>
@@ -18161,7 +18161,7 @@
         <v>0</v>
       </c>
       <c r="F274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G274" t="str">
         <v>ARCRED</v>
@@ -18226,7 +18226,7 @@
         <v>0</v>
       </c>
       <c r="F275">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G275" t="str">
         <v>ARCRED</v>
@@ -18291,7 +18291,7 @@
         <v>0</v>
       </c>
       <c r="F276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G276" t="str">
         <v>ARCRED</v>
@@ -18356,7 +18356,7 @@
         <v>56</v>
       </c>
       <c r="F277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G277" t="str">
         <v>Astralis</v>
@@ -18421,7 +18421,7 @@
         <v>56</v>
       </c>
       <c r="F278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G278" t="str">
         <v>Astralis</v>
@@ -18486,7 +18486,7 @@
         <v>56</v>
       </c>
       <c r="F279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G279" t="str">
         <v>Astralis</v>
@@ -18551,7 +18551,7 @@
         <v>56</v>
       </c>
       <c r="F280">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G280" t="str">
         <v>Astralis</v>
@@ -18616,7 +18616,7 @@
         <v>56</v>
       </c>
       <c r="F281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G281" t="str">
         <v>Astralis</v>
@@ -18681,7 +18681,7 @@
         <v>0</v>
       </c>
       <c r="F282">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G282" t="str">
         <v>ShindeN</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="F283">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G283" t="str">
         <v>ShindeN</v>
@@ -18811,7 +18811,7 @@
         <v>0</v>
       </c>
       <c r="F284">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G284" t="str">
         <v>ShindeN</v>
@@ -18876,7 +18876,7 @@
         <v>0</v>
       </c>
       <c r="F285">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G285" t="str">
         <v>ShindeN</v>
@@ -18941,7 +18941,7 @@
         <v>0</v>
       </c>
       <c r="F286">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G286" t="str">
         <v>ShindeN</v>
@@ -19006,7 +19006,7 @@
         <v>0</v>
       </c>
       <c r="F287">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G287" t="str">
         <v>Permitta</v>
@@ -19071,7 +19071,7 @@
         <v>0</v>
       </c>
       <c r="F288">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G288" t="str">
         <v>Permitta</v>
@@ -19136,7 +19136,7 @@
         <v>0</v>
       </c>
       <c r="F289">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G289" t="str">
         <v>Permitta</v>
@@ -19201,7 +19201,7 @@
         <v>0</v>
       </c>
       <c r="F290">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G290" t="str">
         <v>Permitta</v>
@@ -19266,7 +19266,7 @@
         <v>0</v>
       </c>
       <c r="F291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G291" t="str">
         <v>Permitta</v>
@@ -19331,7 +19331,7 @@
         <v>3811.428571428571</v>
       </c>
       <c r="F292">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G292" t="str">
         <v>Fnatic</v>
@@ -19396,7 +19396,7 @@
         <v>5240</v>
       </c>
       <c r="F293">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G293" t="str">
         <v>Fnatic</v>
@@ -19461,7 +19461,7 @@
         <v>2382.8571428571427</v>
       </c>
       <c r="F294">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G294" t="str">
         <v>Fnatic</v>
@@ -19526,7 +19526,7 @@
         <v>240</v>
       </c>
       <c r="F295">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G295" t="str">
         <v>Fnatic</v>
@@ -19591,7 +19591,7 @@
         <v>240</v>
       </c>
       <c r="F296">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G296" t="str">
         <v>Fnatic</v>
@@ -19656,7 +19656,7 @@
         <v>0</v>
       </c>
       <c r="F297">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G297" t="str">
         <v>ENCE</v>
@@ -19721,7 +19721,7 @@
         <v>0</v>
       </c>
       <c r="F298">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G298" t="str">
         <v>ENCE</v>
@@ -19786,7 +19786,7 @@
         <v>0</v>
       </c>
       <c r="F299">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G299" t="str">
         <v>ENCE</v>
@@ -19851,7 +19851,7 @@
         <v>0</v>
       </c>
       <c r="F300">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G300" t="str">
         <v>ENCE</v>
@@ -19916,7 +19916,7 @@
         <v>0</v>
       </c>
       <c r="F301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G301" t="str">
         <v>ENCE</v>
@@ -19981,7 +19981,7 @@
         <v>0</v>
       </c>
       <c r="F302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G302" t="str">
         <v>Dignitas</v>
@@ -20046,7 +20046,7 @@
         <v>0</v>
       </c>
       <c r="F303">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G303" t="str">
         <v>Dignitas</v>
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="F304">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G304" t="str">
         <v>Dignitas</v>
@@ -20176,7 +20176,7 @@
         <v>0</v>
       </c>
       <c r="F305">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G305" t="str">
         <v>Dignitas</v>
@@ -20241,7 +20241,7 @@
         <v>0</v>
       </c>
       <c r="F306">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G306" t="str">
         <v>Dignitas</v>
@@ -20306,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="F307">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G307" t="str">
         <v>iBUYPOWER</v>
@@ -20371,7 +20371,7 @@
         <v>0</v>
       </c>
       <c r="F308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G308" t="str">
         <v>iBUYPOWER</v>
@@ -20436,7 +20436,7 @@
         <v>0</v>
       </c>
       <c r="F309">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G309" t="str">
         <v>iBUYPOWER</v>
@@ -20501,7 +20501,7 @@
         <v>0</v>
       </c>
       <c r="F310">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G310" t="str">
         <v>iBUYPOWER</v>
@@ -20566,7 +20566,7 @@
         <v>0</v>
       </c>
       <c r="F311">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G311" t="str">
         <v>iBUYPOWER</v>
@@ -20631,7 +20631,7 @@
         <v>0</v>
       </c>
       <c r="F312">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G312" t="str">
         <v>3DMAX</v>
@@ -20696,7 +20696,7 @@
         <v>0</v>
       </c>
       <c r="F313">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G313" t="str">
         <v>3DMAX</v>
@@ -20761,7 +20761,7 @@
         <v>0</v>
       </c>
       <c r="F314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G314" t="str">
         <v>3DMAX</v>
@@ -20826,7 +20826,7 @@
         <v>0</v>
       </c>
       <c r="F315">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G315" t="str">
         <v>3DMAX</v>
@@ -20891,7 +20891,7 @@
         <v>0</v>
       </c>
       <c r="F316">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G316" t="str">
         <v>3DMAX</v>
@@ -20956,7 +20956,7 @@
         <v>800</v>
       </c>
       <c r="F317">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G317" t="str">
         <v>G2</v>
@@ -21021,7 +21021,7 @@
         <v>800</v>
       </c>
       <c r="F318">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G318" t="str">
         <v>G2</v>
@@ -21086,7 +21086,7 @@
         <v>800</v>
       </c>
       <c r="F319">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G319" t="str">
         <v>G2</v>
@@ -21151,7 +21151,7 @@
         <v>800</v>
       </c>
       <c r="F320">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G320" t="str">
         <v>G2</v>
@@ -21216,7 +21216,7 @@
         <v>800</v>
       </c>
       <c r="F321">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G321" t="str">
         <v>G2</v>
@@ -21281,7 +21281,7 @@
         <v>2000</v>
       </c>
       <c r="F322">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G322" t="str">
         <v>Eternal Fire</v>
@@ -21346,7 +21346,7 @@
         <v>2000</v>
       </c>
       <c r="F323">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G323" t="str">
         <v>Eternal Fire</v>
@@ -21411,7 +21411,7 @@
         <v>2000</v>
       </c>
       <c r="F324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G324" t="str">
         <v>Eternal Fire</v>
@@ -21476,7 +21476,7 @@
         <v>2000</v>
       </c>
       <c r="F325">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G325" t="str">
         <v>Eternal Fire</v>
@@ -21541,7 +21541,7 @@
         <v>2000</v>
       </c>
       <c r="F326">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G326" t="str">
         <v>Eternal Fire</v>
@@ -21606,7 +21606,7 @@
         <v>0</v>
       </c>
       <c r="F327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G327" t="str">
         <v>Spirit Academy</v>
@@ -21671,7 +21671,7 @@
         <v>0</v>
       </c>
       <c r="F328">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G328" t="str">
         <v>Spirit Academy</v>
@@ -21736,7 +21736,7 @@
         <v>0</v>
       </c>
       <c r="F329">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G329" t="str">
         <v>Spirit Academy</v>
@@ -21801,7 +21801,7 @@
         <v>0</v>
       </c>
       <c r="F330">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G330" t="str">
         <v>Spirit Academy</v>
@@ -21866,7 +21866,7 @@
         <v>0</v>
       </c>
       <c r="F331">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G331" t="str">
         <v>Spirit Academy</v>
@@ -21931,7 +21931,7 @@
         <v>0</v>
       </c>
       <c r="F332">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G332" t="str">
         <v>Tricked</v>
@@ -21996,7 +21996,7 @@
         <v>0</v>
       </c>
       <c r="F333">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G333" t="str">
         <v>Tricked</v>
@@ -22061,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="F334">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G334" t="str">
         <v>Tricked</v>
@@ -22126,7 +22126,7 @@
         <v>0</v>
       </c>
       <c r="F335">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G335" t="str">
         <v>Tricked</v>
@@ -22191,7 +22191,7 @@
         <v>0</v>
       </c>
       <c r="F336">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G336" t="str">
         <v>Tricked</v>
@@ -22256,7 +22256,7 @@
         <v>56</v>
       </c>
       <c r="F337">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G337" t="str">
         <v>Lynn Vision</v>
@@ -22321,7 +22321,7 @@
         <v>56</v>
       </c>
       <c r="F338">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G338" t="str">
         <v>Lynn Vision</v>
@@ -22386,7 +22386,7 @@
         <v>56</v>
       </c>
       <c r="F339">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G339" t="str">
         <v>Lynn Vision</v>
@@ -22451,7 +22451,7 @@
         <v>56</v>
       </c>
       <c r="F340">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G340" t="str">
         <v>Lynn Vision</v>
@@ -22516,7 +22516,7 @@
         <v>56</v>
       </c>
       <c r="F341">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G341" t="str">
         <v>Lynn Vision</v>
@@ -22581,7 +22581,7 @@
         <v>3600</v>
       </c>
       <c r="F342">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G342" t="str">
         <v>Nemiga</v>
@@ -22646,7 +22646,7 @@
         <v>3600</v>
       </c>
       <c r="F343">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G343" t="str">
         <v>Nemiga</v>
@@ -22711,7 +22711,7 @@
         <v>3600</v>
       </c>
       <c r="F344">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G344" t="str">
         <v>Nemiga</v>
@@ -22776,7 +22776,7 @@
         <v>3600</v>
       </c>
       <c r="F345">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G345" t="str">
         <v>Nemiga</v>
@@ -22841,7 +22841,7 @@
         <v>3600</v>
       </c>
       <c r="F346">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G346" t="str">
         <v>Nemiga</v>
@@ -22906,7 +22906,7 @@
         <v>0</v>
       </c>
       <c r="F347">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G347" t="str">
         <v>Wings Up</v>
@@ -22971,7 +22971,7 @@
         <v>0</v>
       </c>
       <c r="F348">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G348" t="str">
         <v>Wings Up</v>
@@ -23036,7 +23036,7 @@
         <v>0</v>
       </c>
       <c r="F349">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G349" t="str">
         <v>Wings Up</v>
@@ -23101,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="F350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G350" t="str">
         <v>Wings Up</v>
@@ -23166,7 +23166,7 @@
         <v>0</v>
       </c>
       <c r="F351">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G351" t="str">
         <v>Wings Up</v>
@@ -23231,7 +23231,7 @@
         <v>800</v>
       </c>
       <c r="F352">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G352" t="str">
         <v>NAVI Junior</v>
@@ -23296,7 +23296,7 @@
         <v>800</v>
       </c>
       <c r="F353">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G353" t="str">
         <v>NAVI Junior</v>
@@ -23361,7 +23361,7 @@
         <v>800</v>
       </c>
       <c r="F354">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G354" t="str">
         <v>NAVI Junior</v>
@@ -23426,7 +23426,7 @@
         <v>800</v>
       </c>
       <c r="F355">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G355" t="str">
         <v>NAVI Junior</v>
@@ -23491,7 +23491,7 @@
         <v>800</v>
       </c>
       <c r="F356">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G356" t="str">
         <v>NAVI Junior</v>
@@ -23556,7 +23556,7 @@
         <v>2262.8571428571427</v>
       </c>
       <c r="F357">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G357" t="str">
         <v>BC.Game</v>
@@ -23621,7 +23621,7 @@
         <v>120</v>
       </c>
       <c r="F358">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G358" t="str">
         <v>BC.Game</v>
@@ -23674,7 +23674,7 @@
         <v>Valiance</v>
       </c>
       <c r="B359" t="str">
-        <v>Starter</v>
+        <v/>
       </c>
       <c r="C359" t="str">
         <v>rifler</v>
@@ -23686,10 +23686,10 @@
         <v>120</v>
       </c>
       <c r="F359">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G359" t="str">
-        <v>BC.Game</v>
+        <v>none</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -23728,7 +23728,7 @@
         <v>0</v>
       </c>
       <c r="T359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U359" t="str">
         <v/>
@@ -23751,7 +23751,7 @@
         <v>120</v>
       </c>
       <c r="F360">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G360" t="str">
         <v>BC.Game</v>
@@ -23816,7 +23816,7 @@
         <v>120</v>
       </c>
       <c r="F361">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G361" t="str">
         <v>BC.Game</v>
@@ -23881,7 +23881,7 @@
         <v>1200</v>
       </c>
       <c r="F362">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G362" t="str">
         <v>PARIVISION</v>
@@ -23946,7 +23946,7 @@
         <v>1200</v>
       </c>
       <c r="F363">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G363" t="str">
         <v>PARIVISION</v>
@@ -24011,7 +24011,7 @@
         <v>1200</v>
       </c>
       <c r="F364">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G364" t="str">
         <v>PARIVISION</v>
@@ -24076,7 +24076,7 @@
         <v>1200</v>
       </c>
       <c r="F365">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G365" t="str">
         <v>PARIVISION</v>
@@ -24141,7 +24141,7 @@
         <v>1200</v>
       </c>
       <c r="F366">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G366" t="str">
         <v>PARIVISION</v>
@@ -24206,7 +24206,7 @@
         <v>0</v>
       </c>
       <c r="F367">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G367" t="str">
         <v>Skinvault</v>
@@ -24271,7 +24271,7 @@
         <v>0</v>
       </c>
       <c r="F368">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G368" t="str">
         <v>Skinvault</v>
@@ -24336,7 +24336,7 @@
         <v>0</v>
       </c>
       <c r="F369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G369" t="str">
         <v>Skinvault</v>
@@ -24401,7 +24401,7 @@
         <v>0</v>
       </c>
       <c r="F370">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G370" t="str">
         <v>Skinvault</v>
@@ -24466,7 +24466,7 @@
         <v>0</v>
       </c>
       <c r="F371">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G371" t="str">
         <v>Skinvault</v>
@@ -24531,7 +24531,7 @@
         <v>0</v>
       </c>
       <c r="F372">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G372" t="str">
         <v>Alliance</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="F373">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G373" t="str">
         <v>Alliance</v>
@@ -24661,7 +24661,7 @@
         <v>0</v>
       </c>
       <c r="F374">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G374" t="str">
         <v>Alliance</v>
@@ -24726,7 +24726,7 @@
         <v>0</v>
       </c>
       <c r="F375">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G375" t="str">
         <v>Alliance</v>
@@ -24791,7 +24791,7 @@
         <v>0</v>
       </c>
       <c r="F376">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G376" t="str">
         <v>Alliance</v>
@@ -24856,7 +24856,7 @@
         <v>0</v>
       </c>
       <c r="F377">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G377" t="str">
         <v>ATOX</v>
@@ -24921,7 +24921,7 @@
         <v>0</v>
       </c>
       <c r="F378">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G378" t="str">
         <v>ATOX</v>
@@ -24986,7 +24986,7 @@
         <v>0</v>
       </c>
       <c r="F379">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G379" t="str">
         <v>ATOX</v>
@@ -25051,7 +25051,7 @@
         <v>0</v>
       </c>
       <c r="F380">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G380" t="str">
         <v>ATOX</v>
@@ -25116,7 +25116,7 @@
         <v>0</v>
       </c>
       <c r="F381">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G381" t="str">
         <v>ATOX</v>
@@ -25181,7 +25181,7 @@
         <v>800</v>
       </c>
       <c r="F382">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G382" t="str">
         <v>TALON</v>
@@ -25246,7 +25246,7 @@
         <v>800</v>
       </c>
       <c r="F383">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G383" t="str">
         <v>TALON</v>
@@ -25311,7 +25311,7 @@
         <v>800</v>
       </c>
       <c r="F384">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G384" t="str">
         <v>TALON</v>
@@ -25376,7 +25376,7 @@
         <v>800</v>
       </c>
       <c r="F385">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G385" t="str">
         <v>TALON</v>
@@ -25441,7 +25441,7 @@
         <v>800</v>
       </c>
       <c r="F386">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G386" t="str">
         <v>TALON</v>
@@ -25506,7 +25506,7 @@
         <v>0</v>
       </c>
       <c r="F387">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G387" t="str">
         <v>Chinggis Warriors</v>
@@ -25571,7 +25571,7 @@
         <v>0</v>
       </c>
       <c r="F388">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G388" t="str">
         <v>Chinggis Warriors</v>
@@ -25636,7 +25636,7 @@
         <v>0</v>
       </c>
       <c r="F389">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G389" t="str">
         <v>Chinggis Warriors</v>
@@ -25701,7 +25701,7 @@
         <v>0</v>
       </c>
       <c r="F390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G390" t="str">
         <v>Chinggis Warriors</v>
@@ -25766,7 +25766,7 @@
         <v>0</v>
       </c>
       <c r="F391">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G391" t="str">
         <v>Chinggis Warriors</v>
@@ -25831,7 +25831,7 @@
         <v>0</v>
       </c>
       <c r="F392">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G392" t="str">
         <v>Vantage</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="F393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G393" t="str">
         <v>Vantage</v>
@@ -25961,7 +25961,7 @@
         <v>0</v>
       </c>
       <c r="F394">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G394" t="str">
         <v>Vantage</v>
@@ -26026,7 +26026,7 @@
         <v>0</v>
       </c>
       <c r="F395">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G395" t="str">
         <v>Vantage</v>
@@ -26091,7 +26091,7 @@
         <v>0</v>
       </c>
       <c r="F396">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G396" t="str">
         <v>Vantage</v>
@@ -26156,7 +26156,7 @@
         <v>0</v>
       </c>
       <c r="F397">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G397" t="str">
         <v>Virtus.pro</v>
@@ -26221,7 +26221,7 @@
         <v>0</v>
       </c>
       <c r="F398">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G398" t="str">
         <v>Virtus.pro</v>
@@ -26286,7 +26286,7 @@
         <v>0</v>
       </c>
       <c r="F399">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G399" t="str">
         <v>Virtus.pro</v>
@@ -26351,7 +26351,7 @@
         <v>0</v>
       </c>
       <c r="F400">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G400" t="str">
         <v>Virtus.pro</v>
@@ -26416,7 +26416,7 @@
         <v>0</v>
       </c>
       <c r="F401">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G401" t="str">
         <v>Virtus.pro</v>
@@ -26481,7 +26481,7 @@
         <v>0</v>
       </c>
       <c r="F402">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G402" t="str">
         <v>Evil Geniuses</v>
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="F403">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G403" t="str">
         <v>Evil Geniuses</v>
@@ -26611,7 +26611,7 @@
         <v>0</v>
       </c>
       <c r="F404">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G404" t="str">
         <v>Evil Geniuses</v>
@@ -26676,7 +26676,7 @@
         <v>0</v>
       </c>
       <c r="F405">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G405" t="str">
         <v>Evil Geniuses</v>
@@ -26741,7 +26741,7 @@
         <v>0</v>
       </c>
       <c r="F406">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G406" t="str">
         <v>Evil Geniuses</v>
@@ -26806,7 +26806,7 @@
         <v>56</v>
       </c>
       <c r="F407">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G407" t="str">
         <v>Take Flyte</v>
@@ -26871,7 +26871,7 @@
         <v>56</v>
       </c>
       <c r="F408">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G408" t="str">
         <v>Take Flyte</v>
@@ -26936,7 +26936,7 @@
         <v>56</v>
       </c>
       <c r="F409">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G409" t="str">
         <v>Take Flyte</v>
@@ -27001,7 +27001,7 @@
         <v>56</v>
       </c>
       <c r="F410">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G410" t="str">
         <v>Take Flyte</v>
@@ -27066,7 +27066,7 @@
         <v>56</v>
       </c>
       <c r="F411">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G411" t="str">
         <v>Take Flyte</v>
@@ -27131,7 +27131,7 @@
         <v>0</v>
       </c>
       <c r="F412">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G412" t="str">
         <v>Carnival</v>
@@ -27196,7 +27196,7 @@
         <v>0</v>
       </c>
       <c r="F413">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G413" t="str">
         <v>Carnival</v>
@@ -27261,7 +27261,7 @@
         <v>0</v>
       </c>
       <c r="F414">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G414" t="str">
         <v>Carnival</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="F415">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G415" t="str">
         <v>Carnival</v>
@@ -27391,7 +27391,7 @@
         <v>0</v>
       </c>
       <c r="F416">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G416" t="str">
         <v>Carnival</v>
@@ -27456,7 +27456,7 @@
         <v>0</v>
       </c>
       <c r="F417">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G417" t="str">
         <v>CatEvil</v>
@@ -27521,7 +27521,7 @@
         <v>0</v>
       </c>
       <c r="F418">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G418" t="str">
         <v>CatEvil</v>
@@ -27586,7 +27586,7 @@
         <v>0</v>
       </c>
       <c r="F419">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G419" t="str">
         <v>CatEvil</v>
@@ -27651,7 +27651,7 @@
         <v>0</v>
       </c>
       <c r="F420">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G420" t="str">
         <v>CatEvil</v>
@@ -27716,7 +27716,7 @@
         <v>0</v>
       </c>
       <c r="F421">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G421" t="str">
         <v>CatEvil</v>
@@ -27781,7 +27781,7 @@
         <v>0</v>
       </c>
       <c r="F422">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G422" t="str">
         <v>Aravt</v>
@@ -27846,7 +27846,7 @@
         <v>0</v>
       </c>
       <c r="F423">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G423" t="str">
         <v>Aravt</v>
@@ -27911,7 +27911,7 @@
         <v>0</v>
       </c>
       <c r="F424">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G424" t="str">
         <v>Aravt</v>
@@ -27976,7 +27976,7 @@
         <v>0</v>
       </c>
       <c r="F425">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G425" t="str">
         <v>Aravt</v>
@@ -28041,7 +28041,7 @@
         <v>0</v>
       </c>
       <c r="F426">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G426" t="str">
         <v>Aravt</v>
@@ -28106,7 +28106,7 @@
         <v>0</v>
       </c>
       <c r="F427">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G427" t="str">
         <v>Gods Reign</v>
@@ -28171,7 +28171,7 @@
         <v>0</v>
       </c>
       <c r="F428">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G428" t="str">
         <v>Gods Reign</v>
@@ -28236,7 +28236,7 @@
         <v>0</v>
       </c>
       <c r="F429">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G429" t="str">
         <v>Gods Reign</v>
@@ -28301,7 +28301,7 @@
         <v>0</v>
       </c>
       <c r="F430">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G430" t="str">
         <v>Gods Reign</v>
@@ -28366,7 +28366,7 @@
         <v>0</v>
       </c>
       <c r="F431">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G431" t="str">
         <v>Gods Reign</v>
@@ -28431,7 +28431,7 @@
         <v>0</v>
       </c>
       <c r="F432">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G432" t="str">
         <v>9Pandas</v>
@@ -28496,7 +28496,7 @@
         <v>0</v>
       </c>
       <c r="F433">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G433" t="str">
         <v>9Pandas</v>
@@ -28561,7 +28561,7 @@
         <v>0</v>
       </c>
       <c r="F434">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G434" t="str">
         <v>9Pandas</v>
@@ -28626,7 +28626,7 @@
         <v>0</v>
       </c>
       <c r="F435">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G435" t="str">
         <v>9Pandas</v>
@@ -28691,7 +28691,7 @@
         <v>0</v>
       </c>
       <c r="F436">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G436" t="str">
         <v>9Pandas</v>
@@ -28756,7 +28756,7 @@
         <v>800</v>
       </c>
       <c r="F437">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G437" t="str">
         <v>BESTIA</v>
@@ -28821,7 +28821,7 @@
         <v>800</v>
       </c>
       <c r="F438">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G438" t="str">
         <v>BESTIA</v>
@@ -28886,7 +28886,7 @@
         <v>800</v>
       </c>
       <c r="F439">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G439" t="str">
         <v>BESTIA</v>
@@ -28951,7 +28951,7 @@
         <v>800</v>
       </c>
       <c r="F440">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G440" t="str">
         <v>BESTIA</v>
@@ -29016,7 +29016,7 @@
         <v>800</v>
       </c>
       <c r="F441">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G441" t="str">
         <v>BESTIA</v>
@@ -29081,7 +29081,7 @@
         <v>0</v>
       </c>
       <c r="F442">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G442" t="str">
         <v>VP.Prodigy</v>
@@ -29146,7 +29146,7 @@
         <v>0</v>
       </c>
       <c r="F443">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G443" t="str">
         <v>VP.Prodigy</v>
@@ -29211,7 +29211,7 @@
         <v>0</v>
       </c>
       <c r="F444">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G444" t="str">
         <v>VP.Prodigy</v>
@@ -29276,7 +29276,7 @@
         <v>0</v>
       </c>
       <c r="F445">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G445" t="str">
         <v>VP.Prodigy</v>
@@ -29341,7 +29341,7 @@
         <v>0</v>
       </c>
       <c r="F446">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G446" t="str">
         <v>VP.Prodigy</v>
@@ -29406,7 +29406,7 @@
         <v>0</v>
       </c>
       <c r="F447">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G447" t="str">
         <v>Sangal</v>
@@ -29471,7 +29471,7 @@
         <v>0</v>
       </c>
       <c r="F448">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G448" t="str">
         <v>Sangal</v>
@@ -29536,7 +29536,7 @@
         <v>0</v>
       </c>
       <c r="F449">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G449" t="str">
         <v>Sangal</v>
@@ -29601,7 +29601,7 @@
         <v>0</v>
       </c>
       <c r="F450">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G450" t="str">
         <v>Sangal</v>
@@ -29666,7 +29666,7 @@
         <v>0</v>
       </c>
       <c r="F451">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G451" t="str">
         <v>Sangal</v>
@@ -29731,7 +29731,7 @@
         <v>0</v>
       </c>
       <c r="F452">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G452" t="str">
         <v>inSanitY</v>
@@ -29796,7 +29796,7 @@
         <v>0</v>
       </c>
       <c r="F453">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G453" t="str">
         <v>inSanitY</v>
@@ -29861,7 +29861,7 @@
         <v>0</v>
       </c>
       <c r="F454">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G454" t="str">
         <v>inSanitY</v>
@@ -29926,7 +29926,7 @@
         <v>0</v>
       </c>
       <c r="F455">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G455" t="str">
         <v>inSanitY</v>
@@ -29991,7 +29991,7 @@
         <v>0</v>
       </c>
       <c r="F456">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G456" t="str">
         <v>inSanitY</v>
@@ -30056,7 +30056,7 @@
         <v>0</v>
       </c>
       <c r="F457">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G457" t="str">
         <v>Solid</v>
@@ -30121,7 +30121,7 @@
         <v>0</v>
       </c>
       <c r="F458">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G458" t="str">
         <v>Solid</v>
@@ -30186,7 +30186,7 @@
         <v>0</v>
       </c>
       <c r="F459">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G459" t="str">
         <v>Solid</v>
@@ -30251,7 +30251,7 @@
         <v>0</v>
       </c>
       <c r="F460">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G460" t="str">
         <v>Solid</v>
@@ -30316,7 +30316,7 @@
         <v>0</v>
       </c>
       <c r="F461">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G461" t="str">
         <v>Solid</v>
@@ -30381,7 +30381,7 @@
         <v>1200</v>
       </c>
       <c r="F462">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G462" t="str">
         <v>Onyx Ravens</v>
@@ -30446,7 +30446,7 @@
         <v>1200</v>
       </c>
       <c r="F463">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G463" t="str">
         <v>Onyx Ravens</v>
@@ -30511,7 +30511,7 @@
         <v>1200</v>
       </c>
       <c r="F464">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G464" t="str">
         <v>Onyx Ravens</v>
@@ -30576,7 +30576,7 @@
         <v>1200</v>
       </c>
       <c r="F465">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G465" t="str">
         <v>Onyx Ravens</v>
@@ -30641,7 +30641,7 @@
         <v>1200</v>
       </c>
       <c r="F466">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G466" t="str">
         <v>Onyx Ravens</v>
@@ -30706,7 +30706,7 @@
         <v>0</v>
       </c>
       <c r="F467">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G467" t="str">
         <v>Qiang</v>
@@ -30771,7 +30771,7 @@
         <v>0</v>
       </c>
       <c r="F468">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G468" t="str">
         <v>Qiang</v>
@@ -30836,7 +30836,7 @@
         <v>0</v>
       </c>
       <c r="F469">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G469" t="str">
         <v>Qiang</v>
@@ -30901,7 +30901,7 @@
         <v>0</v>
       </c>
       <c r="F470">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G470" t="str">
         <v>Qiang</v>
@@ -30966,7 +30966,7 @@
         <v>0</v>
       </c>
       <c r="F471">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G471" t="str">
         <v>Qiang</v>
@@ -31031,7 +31031,7 @@
         <v>0</v>
       </c>
       <c r="F472">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G472" t="str">
         <v>ODDIK</v>
@@ -31096,7 +31096,7 @@
         <v>0</v>
       </c>
       <c r="F473">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G473" t="str">
         <v>ODDIK</v>
@@ -31161,7 +31161,7 @@
         <v>0</v>
       </c>
       <c r="F474">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G474" t="str">
         <v>ODDIK</v>
@@ -31226,7 +31226,7 @@
         <v>0</v>
       </c>
       <c r="F475">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G475" t="str">
         <v>ODDIK</v>
@@ -31291,7 +31291,7 @@
         <v>0</v>
       </c>
       <c r="F476">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G476" t="str">
         <v>ODDIK</v>
@@ -31356,7 +31356,7 @@
         <v>3600</v>
       </c>
       <c r="F477">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G477" t="str">
         <v>Natus Vincere</v>
@@ -31421,7 +31421,7 @@
         <v>3600</v>
       </c>
       <c r="F478">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G478" t="str">
         <v>Natus Vincere</v>
@@ -31486,7 +31486,7 @@
         <v>3600</v>
       </c>
       <c r="F479">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G479" t="str">
         <v>Natus Vincere</v>
@@ -31551,7 +31551,7 @@
         <v>3600</v>
       </c>
       <c r="F480">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G480" t="str">
         <v>Natus Vincere</v>
@@ -31616,7 +31616,7 @@
         <v>3600</v>
       </c>
       <c r="F481">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G481" t="str">
         <v>Natus Vincere</v>
@@ -31681,7 +31681,7 @@
         <v>0</v>
       </c>
       <c r="F482">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G482" t="str">
         <v>True Rippers</v>
@@ -31746,7 +31746,7 @@
         <v>0</v>
       </c>
       <c r="F483">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G483" t="str">
         <v>True Rippers</v>
@@ -31811,7 +31811,7 @@
         <v>0</v>
       </c>
       <c r="F484">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G484" t="str">
         <v>True Rippers</v>
@@ -31876,7 +31876,7 @@
         <v>0</v>
       </c>
       <c r="F485">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G485" t="str">
         <v>True Rippers</v>
@@ -31941,7 +31941,7 @@
         <v>0</v>
       </c>
       <c r="F486">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G486" t="str">
         <v>True Rippers</v>
@@ -32006,7 +32006,7 @@
         <v>0</v>
       </c>
       <c r="F487">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G487" t="str">
         <v>Victores Sumus</v>
@@ -32071,7 +32071,7 @@
         <v>0</v>
       </c>
       <c r="F488">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G488" t="str">
         <v>Victores Sumus</v>
@@ -32136,7 +32136,7 @@
         <v>0</v>
       </c>
       <c r="F489">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G489" t="str">
         <v>Victores Sumus</v>
@@ -32201,7 +32201,7 @@
         <v>0</v>
       </c>
       <c r="F490">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G490" t="str">
         <v>Victores Sumus</v>
@@ -32266,7 +32266,7 @@
         <v>0</v>
       </c>
       <c r="F491">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G491" t="str">
         <v>Victores Sumus</v>
@@ -32331,7 +32331,7 @@
         <v>0</v>
       </c>
       <c r="F492">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G492" t="str">
         <v>The Dice</v>
@@ -32396,7 +32396,7 @@
         <v>0</v>
       </c>
       <c r="F493">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G493" t="str">
         <v>The Dice</v>
@@ -32461,7 +32461,7 @@
         <v>0</v>
       </c>
       <c r="F494">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G494" t="str">
         <v>The Dice</v>
@@ -32526,7 +32526,7 @@
         <v>0</v>
       </c>
       <c r="F495">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G495" t="str">
         <v>The Dice</v>
@@ -32591,7 +32591,7 @@
         <v>0</v>
       </c>
       <c r="F496">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G496" t="str">
         <v>The Dice</v>
@@ -32656,7 +32656,7 @@
         <v>0</v>
       </c>
       <c r="F497">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G497" t="str">
         <v>TYLOO</v>
@@ -32721,7 +32721,7 @@
         <v>0</v>
       </c>
       <c r="F498">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G498" t="str">
         <v>TYLOO</v>
@@ -32786,7 +32786,7 @@
         <v>0</v>
       </c>
       <c r="F499">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G499" t="str">
         <v>TYLOO</v>
@@ -32851,7 +32851,7 @@
         <v>0</v>
       </c>
       <c r="F500">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G500" t="str">
         <v>TYLOO</v>
@@ -32916,7 +32916,7 @@
         <v>0</v>
       </c>
       <c r="F501">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G501" t="str">
         <v>TYLOO</v>
@@ -32981,7 +32981,7 @@
         <v>0</v>
       </c>
       <c r="F502">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G502" t="str">
         <v>Red Viperz</v>
@@ -33046,7 +33046,7 @@
         <v>0</v>
       </c>
       <c r="F503">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G503" t="str">
         <v>Red Viperz</v>
@@ -33111,7 +33111,7 @@
         <v>0</v>
       </c>
       <c r="F504">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G504" t="str">
         <v>Red Viperz</v>
@@ -33176,7 +33176,7 @@
         <v>0</v>
       </c>
       <c r="F505">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G505" t="str">
         <v>Red Viperz</v>
@@ -33241,7 +33241,7 @@
         <v>0</v>
       </c>
       <c r="F506">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G506" t="str">
         <v>Red Viperz</v>
@@ -33306,7 +33306,7 @@
         <v>0</v>
       </c>
       <c r="F507">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G507" t="str">
         <v>Homyno</v>
@@ -33371,7 +33371,7 @@
         <v>0</v>
       </c>
       <c r="F508">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G508" t="str">
         <v>Homyno</v>
@@ -33436,7 +33436,7 @@
         <v>0</v>
       </c>
       <c r="F509">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G509" t="str">
         <v>Homyno</v>
@@ -33501,7 +33501,7 @@
         <v>0</v>
       </c>
       <c r="F510">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G510" t="str">
         <v>Homyno</v>
@@ -33566,7 +33566,7 @@
         <v>0</v>
       </c>
       <c r="F511">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G511" t="str">
         <v>Homyno</v>
@@ -33631,7 +33631,7 @@
         <v>0</v>
       </c>
       <c r="F512">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G512" t="str">
         <v>Outsiders</v>
@@ -33696,7 +33696,7 @@
         <v>0</v>
       </c>
       <c r="F513">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G513" t="str">
         <v>Outsiders</v>
@@ -33761,7 +33761,7 @@
         <v>0</v>
       </c>
       <c r="F514">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G514" t="str">
         <v>Outsiders</v>
@@ -33826,7 +33826,7 @@
         <v>0</v>
       </c>
       <c r="F515">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G515" t="str">
         <v>Outsiders</v>
@@ -33891,7 +33891,7 @@
         <v>0</v>
       </c>
       <c r="F516">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G516" t="str">
         <v>Outsiders</v>
@@ -33956,7 +33956,7 @@
         <v>0</v>
       </c>
       <c r="F517">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G517" t="str">
         <v>MenaceGG</v>
@@ -34021,7 +34021,7 @@
         <v>0</v>
       </c>
       <c r="F518">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G518" t="str">
         <v>MenaceGG</v>
@@ -34086,7 +34086,7 @@
         <v>0</v>
       </c>
       <c r="F519">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G519" t="str">
         <v>MenaceGG</v>
@@ -34151,7 +34151,7 @@
         <v>0</v>
       </c>
       <c r="F520">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G520" t="str">
         <v>MenaceGG</v>
@@ -34216,7 +34216,7 @@
         <v>0</v>
       </c>
       <c r="F521">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G521" t="str">
         <v>MenaceGG</v>
@@ -34281,7 +34281,7 @@
         <v>0</v>
       </c>
       <c r="F522">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G522" t="str">
         <v>NomadS</v>
@@ -34346,7 +34346,7 @@
         <v>0</v>
       </c>
       <c r="F523">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G523" t="str">
         <v>NomadS</v>
@@ -34411,7 +34411,7 @@
         <v>0</v>
       </c>
       <c r="F524">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G524" t="str">
         <v>NomadS</v>
@@ -34476,7 +34476,7 @@
         <v>0</v>
       </c>
       <c r="F525">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G525" t="str">
         <v>NomadS</v>
@@ -34541,7 +34541,7 @@
         <v>0</v>
       </c>
       <c r="F526">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G526" t="str">
         <v>NomadS</v>
@@ -34606,7 +34606,7 @@
         <v>800</v>
       </c>
       <c r="F527">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G527" t="str">
         <v>hoorai</v>
@@ -34671,7 +34671,7 @@
         <v>800</v>
       </c>
       <c r="F528">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G528" t="str">
         <v>hoorai</v>
@@ -34736,7 +34736,7 @@
         <v>800</v>
       </c>
       <c r="F529">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G529" t="str">
         <v>hoorai</v>
@@ -34801,7 +34801,7 @@
         <v>800</v>
       </c>
       <c r="F530">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G530" t="str">
         <v>hoorai</v>
@@ -34866,7 +34866,7 @@
         <v>800</v>
       </c>
       <c r="F531">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G531" t="str">
         <v>hoorai</v>
@@ -34931,7 +34931,7 @@
         <v>0</v>
       </c>
       <c r="F532">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G532" t="str">
         <v>SAW</v>
@@ -34996,7 +34996,7 @@
         <v>0</v>
       </c>
       <c r="F533">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G533" t="str">
         <v>SAW</v>
@@ -35061,7 +35061,7 @@
         <v>0</v>
       </c>
       <c r="F534">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G534" t="str">
         <v>SAW</v>
@@ -35126,7 +35126,7 @@
         <v>0</v>
       </c>
       <c r="F535">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G535" t="str">
         <v>SAW</v>
@@ -35191,7 +35191,7 @@
         <v>0</v>
       </c>
       <c r="F536">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G536" t="str">
         <v>SAW</v>
@@ -35256,7 +35256,7 @@
         <v>0</v>
       </c>
       <c r="F537">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G537" t="str">
         <v>Reason</v>
@@ -35321,7 +35321,7 @@
         <v>0</v>
       </c>
       <c r="F538">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G538" t="str">
         <v>Reason</v>
@@ -35386,7 +35386,7 @@
         <v>0</v>
       </c>
       <c r="F539">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G539" t="str">
         <v>Reason</v>
@@ -35451,7 +35451,7 @@
         <v>0</v>
       </c>
       <c r="F540">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G540" t="str">
         <v>Reason</v>
@@ -35516,7 +35516,7 @@
         <v>0</v>
       </c>
       <c r="F541">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G541" t="str">
         <v>Reason</v>
@@ -35581,7 +35581,7 @@
         <v>120</v>
       </c>
       <c r="F542">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G542" t="str">
         <v>Entropiq</v>
@@ -35646,7 +35646,7 @@
         <v>120</v>
       </c>
       <c r="F543">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G543" t="str">
         <v>Entropiq</v>
@@ -35711,7 +35711,7 @@
         <v>120</v>
       </c>
       <c r="F544">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G544" t="str">
         <v>Entropiq</v>
@@ -35776,7 +35776,7 @@
         <v>120</v>
       </c>
       <c r="F545">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G545" t="str">
         <v>Entropiq</v>
@@ -35841,7 +35841,7 @@
         <v>120</v>
       </c>
       <c r="F546">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G546" t="str">
         <v>Entropiq</v>
@@ -35906,7 +35906,7 @@
         <v>3600</v>
       </c>
       <c r="F547">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G547" t="str">
         <v>The MongolZ</v>
@@ -35971,7 +35971,7 @@
         <v>3600</v>
       </c>
       <c r="F548">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G548" t="str">
         <v>The MongolZ</v>
@@ -36036,7 +36036,7 @@
         <v>3600</v>
       </c>
       <c r="F549">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G549" t="str">
         <v>The MongolZ</v>
@@ -36101,7 +36101,7 @@
         <v>3600</v>
       </c>
       <c r="F550">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G550" t="str">
         <v>The MongolZ</v>
@@ -36166,7 +36166,7 @@
         <v>3600</v>
       </c>
       <c r="F551">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G551" t="str">
         <v>The MongolZ</v>
@@ -36231,7 +36231,7 @@
         <v>0</v>
       </c>
       <c r="F552">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G552" t="str">
         <v>ad hoc</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="F553">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G553" t="str">
         <v>ad hoc</v>
@@ -36361,7 +36361,7 @@
         <v>0</v>
       </c>
       <c r="F554">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G554" t="str">
         <v>ad hoc</v>
@@ -36426,7 +36426,7 @@
         <v>0</v>
       </c>
       <c r="F555">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G555" t="str">
         <v>ad hoc</v>
@@ -36491,7 +36491,7 @@
         <v>0</v>
       </c>
       <c r="F556">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G556" t="str">
         <v>ad hoc</v>
@@ -36556,7 +36556,7 @@
         <v>0</v>
       </c>
       <c r="F557">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G557" t="str">
         <v>MAD Lions</v>
@@ -36621,7 +36621,7 @@
         <v>0</v>
       </c>
       <c r="F558">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G558" t="str">
         <v>MAD Lions</v>
@@ -36686,7 +36686,7 @@
         <v>0</v>
       </c>
       <c r="F559">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G559" t="str">
         <v>MAD Lions</v>
@@ -36751,7 +36751,7 @@
         <v>0</v>
       </c>
       <c r="F560">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G560" t="str">
         <v>MAD Lions</v>
@@ -36816,7 +36816,7 @@
         <v>0</v>
       </c>
       <c r="F561">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G561" t="str">
         <v>MAD Lions</v>
@@ -36881,7 +36881,7 @@
         <v>56</v>
       </c>
       <c r="F562">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G562" t="str">
         <v>Copenhagen Wolves</v>
@@ -36946,7 +36946,7 @@
         <v>56</v>
       </c>
       <c r="F563">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G563" t="str">
         <v>Copenhagen Wolves</v>
@@ -37011,7 +37011,7 @@
         <v>56</v>
       </c>
       <c r="F564">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G564" t="str">
         <v>Copenhagen Wolves</v>
@@ -37076,7 +37076,7 @@
         <v>56</v>
       </c>
       <c r="F565">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G565" t="str">
         <v>Copenhagen Wolves</v>
@@ -37141,7 +37141,7 @@
         <v>56</v>
       </c>
       <c r="F566">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G566" t="str">
         <v>Copenhagen Wolves</v>
@@ -37206,7 +37206,7 @@
         <v>2262.8571428571427</v>
       </c>
       <c r="F567">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G567" t="str">
         <v>Astana Dragons</v>
@@ -37271,7 +37271,7 @@
         <v>120</v>
       </c>
       <c r="F568">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G568" t="str">
         <v>Astana Dragons</v>
@@ -37336,7 +37336,7 @@
         <v>120</v>
       </c>
       <c r="F569">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G569" t="str">
         <v>Astana Dragons</v>
@@ -37401,7 +37401,7 @@
         <v>120</v>
       </c>
       <c r="F570">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G570" t="str">
         <v>Astana Dragons</v>
@@ -37466,7 +37466,7 @@
         <v>120</v>
       </c>
       <c r="F571">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G571" t="str">
         <v>Astana Dragons</v>
@@ -37531,7 +37531,7 @@
         <v>0</v>
       </c>
       <c r="F572">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G572" t="str">
         <v>VeryGames</v>
@@ -37596,7 +37596,7 @@
         <v>0</v>
       </c>
       <c r="F573">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G573" t="str">
         <v>VeryGames</v>
@@ -37661,7 +37661,7 @@
         <v>0</v>
       </c>
       <c r="F574">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G574" t="str">
         <v>VeryGames</v>
@@ -37726,7 +37726,7 @@
         <v>0</v>
       </c>
       <c r="F575">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G575" t="str">
         <v>VeryGames</v>
@@ -37791,7 +37791,7 @@
         <v>0</v>
       </c>
       <c r="F576">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G576" t="str">
         <v>VeryGames</v>
@@ -37856,7 +37856,7 @@
         <v>0</v>
       </c>
       <c r="F577">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G577" t="str">
         <v>mousesports</v>
@@ -37921,7 +37921,7 @@
         <v>0</v>
       </c>
       <c r="F578">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G578" t="str">
         <v>mousesports</v>
@@ -37986,7 +37986,7 @@
         <v>0</v>
       </c>
       <c r="F579">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G579" t="str">
         <v>mousesports</v>
@@ -38051,7 +38051,7 @@
         <v>0</v>
       </c>
       <c r="F580">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G580" t="str">
         <v>mousesports</v>
@@ -38116,7 +38116,7 @@
         <v>0</v>
       </c>
       <c r="F581">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G581" t="str">
         <v>mousesports</v>
@@ -38181,7 +38181,7 @@
         <v>2302.8571428571427</v>
       </c>
       <c r="F582">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G582" t="str">
         <v>Vox Eminor</v>
@@ -38246,7 +38246,7 @@
         <v>160</v>
       </c>
       <c r="F583">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G583" t="str">
         <v>Vox Eminor</v>
@@ -38311,7 +38311,7 @@
         <v>160</v>
       </c>
       <c r="F584">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G584" t="str">
         <v>Vox Eminor</v>
@@ -38376,7 +38376,7 @@
         <v>160</v>
       </c>
       <c r="F585">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G585" t="str">
         <v>Vox Eminor</v>
@@ -38441,7 +38441,7 @@
         <v>160</v>
       </c>
       <c r="F586">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G586" t="str">
         <v>Vox Eminor</v>
@@ -38506,7 +38506,7 @@
         <v>240</v>
       </c>
       <c r="F587">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G587" t="str">
         <v>LGB</v>
@@ -38571,7 +38571,7 @@
         <v>2382.8571428571427</v>
       </c>
       <c r="F588">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G588" t="str">
         <v>LGB</v>
@@ -38636,7 +38636,7 @@
         <v>240</v>
       </c>
       <c r="F589">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G589" t="str">
         <v>LGB</v>
@@ -38701,7 +38701,7 @@
         <v>240</v>
       </c>
       <c r="F590">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G590" t="str">
         <v>LGB</v>
@@ -38766,7 +38766,7 @@
         <v>240</v>
       </c>
       <c r="F591">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G591" t="str">
         <v>LGB</v>
@@ -38831,7 +38831,7 @@
         <v>0</v>
       </c>
       <c r="F592">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G592" t="str">
         <v>Venom</v>
@@ -38896,7 +38896,7 @@
         <v>0</v>
       </c>
       <c r="F593">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G593" t="str">
         <v>Venom</v>
@@ -38961,7 +38961,7 @@
         <v>0</v>
       </c>
       <c r="F594">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G594" t="str">
         <v>Venom</v>
@@ -39026,7 +39026,7 @@
         <v>0</v>
       </c>
       <c r="F595">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G595" t="str">
         <v>Venom</v>
@@ -39091,7 +39091,7 @@
         <v>0</v>
       </c>
       <c r="F596">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G596" t="str">
         <v>Venom</v>
@@ -39156,7 +39156,7 @@
         <v>0</v>
       </c>
       <c r="F597">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G597" t="str">
         <v>ESC</v>
@@ -39221,7 +39221,7 @@
         <v>0</v>
       </c>
       <c r="F598">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G598" t="str">
         <v>ESC</v>
@@ -39286,7 +39286,7 @@
         <v>0</v>
       </c>
       <c r="F599">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G599" t="str">
         <v>ESC</v>
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="F600">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G600" t="str">
         <v>ESC</v>
@@ -39416,7 +39416,7 @@
         <v>0</v>
       </c>
       <c r="F601">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G601" t="str">
         <v>ESC</v>
@@ -39481,7 +39481,7 @@
         <v>120</v>
       </c>
       <c r="F602">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G602" t="str">
         <v>Bravado</v>
@@ -39546,7 +39546,7 @@
         <v>120</v>
       </c>
       <c r="F603">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G603" t="str">
         <v>Bravado</v>
@@ -39611,7 +39611,7 @@
         <v>120</v>
       </c>
       <c r="F604">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G604" t="str">
         <v>Bravado</v>
@@ -39676,7 +39676,7 @@
         <v>120</v>
       </c>
       <c r="F605">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G605" t="str">
         <v>Bravado</v>
@@ -39741,7 +39741,7 @@
         <v>2262.8571428571427</v>
       </c>
       <c r="F606">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G606" t="str">
         <v>Bravado</v>
@@ -39806,7 +39806,7 @@
         <v>0</v>
       </c>
       <c r="F607">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G607" t="str">
         <v>Kinguin</v>
@@ -39871,7 +39871,7 @@
         <v>0</v>
       </c>
       <c r="F608">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G608" t="str">
         <v>Kinguin</v>
@@ -39936,7 +39936,7 @@
         <v>0</v>
       </c>
       <c r="F609">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G609" t="str">
         <v>Kinguin</v>
@@ -40001,7 +40001,7 @@
         <v>0</v>
       </c>
       <c r="F610">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G610" t="str">
         <v>Kinguin</v>
@@ -40066,7 +40066,7 @@
         <v>0</v>
       </c>
       <c r="F611">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G611" t="str">
         <v>Kinguin</v>
@@ -40131,7 +40131,7 @@
         <v>0</v>
       </c>
       <c r="F612">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G612" t="str">
         <v>Counter Logic</v>
@@ -40196,7 +40196,7 @@
         <v>0</v>
       </c>
       <c r="F613">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G613" t="str">
         <v>Counter Logic</v>
@@ -40261,7 +40261,7 @@
         <v>0</v>
       </c>
       <c r="F614">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G614" t="str">
         <v>Counter Logic</v>
@@ -40326,7 +40326,7 @@
         <v>0</v>
       </c>
       <c r="F615">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G615" t="str">
         <v>Counter Logic</v>
@@ -40391,7 +40391,7 @@
         <v>0</v>
       </c>
       <c r="F616">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G616" t="str">
         <v>Counter Logic</v>
@@ -40456,7 +40456,7 @@
         <v>0</v>
       </c>
       <c r="F617">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G617" t="str">
         <v>Gambit</v>
@@ -40521,7 +40521,7 @@
         <v>0</v>
       </c>
       <c r="F618">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G618" t="str">
         <v>Gambit</v>
@@ -40586,7 +40586,7 @@
         <v>0</v>
       </c>
       <c r="F619">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G619" t="str">
         <v>Gambit</v>
@@ -40651,7 +40651,7 @@
         <v>0</v>
       </c>
       <c r="F620">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G620" t="str">
         <v>Gambit</v>
@@ -40716,7 +40716,7 @@
         <v>0</v>
       </c>
       <c r="F621">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G621" t="str">
         <v>Gambit</v>
@@ -40781,7 +40781,7 @@
         <v>0</v>
       </c>
       <c r="F622">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G622" t="str">
         <v>Space Soldiers</v>
@@ -40846,7 +40846,7 @@
         <v>0</v>
       </c>
       <c r="F623">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G623" t="str">
         <v>Space Soldiers</v>
@@ -40911,7 +40911,7 @@
         <v>0</v>
       </c>
       <c r="F624">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G624" t="str">
         <v>Space Soldiers</v>
@@ -40976,7 +40976,7 @@
         <v>0</v>
       </c>
       <c r="F625">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G625" t="str">
         <v>Space Soldiers</v>
@@ -41041,7 +41041,7 @@
         <v>0</v>
       </c>
       <c r="F626">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G626" t="str">
         <v>Space Soldiers</v>
@@ -41106,7 +41106,7 @@
         <v>0</v>
       </c>
       <c r="F627">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G627" t="str">
         <v>Quantum Bellator Fire</v>
@@ -41171,7 +41171,7 @@
         <v>0</v>
       </c>
       <c r="F628">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G628" t="str">
         <v>Quantum Bellator Fire</v>
@@ -41236,7 +41236,7 @@
         <v>0</v>
       </c>
       <c r="F629">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G629" t="str">
         <v>Quantum Bellator Fire</v>
@@ -41301,7 +41301,7 @@
         <v>0</v>
       </c>
       <c r="F630">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G630" t="str">
         <v>Quantum Bellator Fire</v>
@@ -41366,7 +41366,7 @@
         <v>0</v>
       </c>
       <c r="F631">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G631" t="str">
         <v>Quantum Bellator Fire</v>
@@ -41431,7 +41431,7 @@
         <v>56</v>
       </c>
       <c r="F632">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G632" t="str">
         <v>Avangar</v>
@@ -41496,7 +41496,7 @@
         <v>56</v>
       </c>
       <c r="F633">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G633" t="str">
         <v>Avangar</v>
@@ -41561,7 +41561,7 @@
         <v>56</v>
       </c>
       <c r="F634">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G634" t="str">
         <v>Avangar</v>
@@ -41626,7 +41626,7 @@
         <v>56</v>
       </c>
       <c r="F635">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G635" t="str">
         <v>Avangar</v>
@@ -41691,7 +41691,7 @@
         <v>56</v>
       </c>
       <c r="F636">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G636" t="str">
         <v>Avangar</v>
@@ -41756,7 +41756,7 @@
         <v>0</v>
       </c>
       <c r="F637">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G637" t="str">
         <v>Misfits</v>
@@ -41821,7 +41821,7 @@
         <v>0</v>
       </c>
       <c r="F638">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G638" t="str">
         <v>Misfits</v>
@@ -41886,7 +41886,7 @@
         <v>0</v>
       </c>
       <c r="F639">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G639" t="str">
         <v>Misfits</v>
@@ -41951,7 +41951,7 @@
         <v>0</v>
       </c>
       <c r="F640">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G640" t="str">
         <v>Misfits</v>
@@ -42016,7 +42016,7 @@
         <v>0</v>
       </c>
       <c r="F641">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G641" t="str">
         <v>Misfits</v>
@@ -42081,7 +42081,7 @@
         <v>0</v>
       </c>
       <c r="F642">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G642" t="str">
         <v>Sprout</v>
@@ -42146,7 +42146,7 @@
         <v>0</v>
       </c>
       <c r="F643">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G643" t="str">
         <v>Sprout</v>
@@ -42211,7 +42211,7 @@
         <v>0</v>
       </c>
       <c r="F644">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G644" t="str">
         <v>Sprout</v>
@@ -42276,7 +42276,7 @@
         <v>0</v>
       </c>
       <c r="F645">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G645" t="str">
         <v>Sprout</v>
@@ -42341,7 +42341,7 @@
         <v>0</v>
       </c>
       <c r="F646">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G646" t="str">
         <v>Sprout</v>
@@ -42406,7 +42406,7 @@
         <v>0</v>
       </c>
       <c r="F647">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G647" t="str">
         <v>Flash</v>
@@ -42471,7 +42471,7 @@
         <v>0</v>
       </c>
       <c r="F648">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G648" t="str">
         <v>Flash</v>
@@ -42536,7 +42536,7 @@
         <v>0</v>
       </c>
       <c r="F649">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G649" t="str">
         <v>Flash</v>
@@ -42601,7 +42601,7 @@
         <v>0</v>
       </c>
       <c r="F650">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G650" t="str">
         <v>Flash</v>
@@ -42666,7 +42666,7 @@
         <v>0</v>
       </c>
       <c r="F651">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G651" t="str">
         <v>Flash</v>
@@ -42731,7 +42731,7 @@
         <v>0</v>
       </c>
       <c r="F652">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G652" t="str">
         <v>100 Thieves</v>
@@ -42796,7 +42796,7 @@
         <v>0</v>
       </c>
       <c r="F653">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G653" t="str">
         <v>100 Thieves</v>
@@ -42861,7 +42861,7 @@
         <v>0</v>
       </c>
       <c r="F654">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G654" t="str">
         <v>100 Thieves</v>
@@ -42926,7 +42926,7 @@
         <v>0</v>
       </c>
       <c r="F655">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G655" t="str">
         <v>100 Thieves</v>
@@ -42991,7 +42991,7 @@
         <v>0</v>
       </c>
       <c r="F656">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G656" t="str">
         <v>100 Thieves</v>
@@ -43056,7 +43056,7 @@
         <v>0</v>
       </c>
       <c r="F657">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G657" t="str">
         <v>Immortals</v>
@@ -43121,7 +43121,7 @@
         <v>0</v>
       </c>
       <c r="F658">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G658" t="str">
         <v>Immortals</v>
@@ -43186,7 +43186,7 @@
         <v>0</v>
       </c>
       <c r="F659">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G659" t="str">
         <v>Immortals</v>
@@ -43251,7 +43251,7 @@
         <v>0</v>
       </c>
       <c r="F660">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G660" t="str">
         <v>Immortals</v>
@@ -43316,7 +43316,7 @@
         <v>0</v>
       </c>
       <c r="F661">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G661" t="str">
         <v>Immortals</v>
@@ -43381,7 +43381,7 @@
         <v>56</v>
       </c>
       <c r="F662">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G662" t="str">
         <v>Rogue</v>
@@ -43446,7 +43446,7 @@
         <v>56</v>
       </c>
       <c r="F663">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G663" t="str">
         <v>Rogue</v>
@@ -43511,7 +43511,7 @@
         <v>56</v>
       </c>
       <c r="F664">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G664" t="str">
         <v>Rogue</v>
@@ -43576,7 +43576,7 @@
         <v>56</v>
       </c>
       <c r="F665">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G665" t="str">
         <v>Rogue</v>
@@ -43641,7 +43641,7 @@
         <v>56</v>
       </c>
       <c r="F666">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G666" t="str">
         <v>Rogue</v>
@@ -43706,7 +43706,7 @@
         <v>56</v>
       </c>
       <c r="F667">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G667" t="str">
         <v>FORZE</v>
@@ -43771,7 +43771,7 @@
         <v>56</v>
       </c>
       <c r="F668">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G668" t="str">
         <v>FORZE</v>
@@ -43836,7 +43836,7 @@
         <v>56</v>
       </c>
       <c r="F669">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G669" t="str">
         <v>FORZE</v>
@@ -43901,7 +43901,7 @@
         <v>56</v>
       </c>
       <c r="F670">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G670" t="str">
         <v>FORZE</v>
@@ -43966,7 +43966,7 @@
         <v>56</v>
       </c>
       <c r="F671">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G671" t="str">
         <v>FORZE</v>
@@ -44031,7 +44031,7 @@
         <v>0</v>
       </c>
       <c r="F672">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G672" t="str">
         <v>00 Nation</v>
@@ -44096,7 +44096,7 @@
         <v>0</v>
       </c>
       <c r="F673">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G673" t="str">
         <v>00 Nation</v>
@@ -44161,7 +44161,7 @@
         <v>0</v>
       </c>
       <c r="F674">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G674" t="str">
         <v>00 Nation</v>
@@ -44226,7 +44226,7 @@
         <v>0</v>
       </c>
       <c r="F675">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G675" t="str">
         <v>00 Nation</v>
@@ -44291,7 +44291,7 @@
         <v>0</v>
       </c>
       <c r="F676">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G676" t="str">
         <v>00 Nation</v>
@@ -44356,7 +44356,7 @@
         <v>56</v>
       </c>
       <c r="F677">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G677" t="str">
         <v>Into the Beach</v>
@@ -44421,7 +44421,7 @@
         <v>56</v>
       </c>
       <c r="F678">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G678" t="str">
         <v>Into the Beach</v>
@@ -44486,7 +44486,7 @@
         <v>56</v>
       </c>
       <c r="F679">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G679" t="str">
         <v>Into the Beach</v>
@@ -44551,7 +44551,7 @@
         <v>56</v>
       </c>
       <c r="F680">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G680" t="str">
         <v>Into the Beach</v>
@@ -44616,7 +44616,7 @@
         <v>56</v>
       </c>
       <c r="F681">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G681" t="str">
         <v>Into the Beach</v>
@@ -44681,7 +44681,7 @@
         <v>0</v>
       </c>
       <c r="F682">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G682" t="str">
         <v>Movistar KOI</v>
@@ -44746,7 +44746,7 @@
         <v>0</v>
       </c>
       <c r="F683">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G683" t="str">
         <v>Movistar KOI</v>
@@ -44811,7 +44811,7 @@
         <v>0</v>
       </c>
       <c r="F684">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G684" t="str">
         <v>Movistar KOI</v>
@@ -44876,7 +44876,7 @@
         <v>0</v>
       </c>
       <c r="F685">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G685" t="str">
         <v>Movistar KOI</v>
@@ -44941,7 +44941,7 @@
         <v>0</v>
       </c>
       <c r="F686">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G686" t="str">
         <v>Movistar KOI</v>
@@ -45006,7 +45006,7 @@
         <v>0</v>
       </c>
       <c r="F687">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G687" t="str">
         <v>FLuffy Gangsters</v>
@@ -45071,7 +45071,7 @@
         <v>0</v>
       </c>
       <c r="F688">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G688" t="str">
         <v>FLuffy Gangsters</v>
@@ -45136,7 +45136,7 @@
         <v>0</v>
       </c>
       <c r="F689">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G689" t="str">
         <v>FLuffy Gangsters</v>
@@ -45201,7 +45201,7 @@
         <v>0</v>
       </c>
       <c r="F690">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G690" t="str">
         <v>FLuffy Gangsters</v>
@@ -45266,7 +45266,7 @@
         <v>0</v>
       </c>
       <c r="F691">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G691" t="str">
         <v>FLuffy Gangsters</v>
@@ -45331,7 +45331,7 @@
         <v>800</v>
       </c>
       <c r="F692">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G692" t="str">
         <v>Verdant</v>
@@ -45396,7 +45396,7 @@
         <v>800</v>
       </c>
       <c r="F693">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G693" t="str">
         <v>Verdant</v>
@@ -45461,7 +45461,7 @@
         <v>800</v>
       </c>
       <c r="F694">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G694" t="str">
         <v>Verdant</v>
@@ -45526,7 +45526,7 @@
         <v>800</v>
       </c>
       <c r="F695">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G695" t="str">
         <v>Verdant</v>
@@ -45591,7 +45591,7 @@
         <v>800</v>
       </c>
       <c r="F696">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G696" t="str">
         <v>Verdant</v>
@@ -45656,7 +45656,7 @@
         <v>0</v>
       </c>
       <c r="F697">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G697" t="str">
         <v>NIP Impact</v>
@@ -45721,7 +45721,7 @@
         <v>0</v>
       </c>
       <c r="F698">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G698" t="str">
         <v>NIP Impact</v>
@@ -45786,7 +45786,7 @@
         <v>0</v>
       </c>
       <c r="F699">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G699" t="str">
         <v>NIP Impact</v>
@@ -45851,7 +45851,7 @@
         <v>0</v>
       </c>
       <c r="F700">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G700" t="str">
         <v>NIP Impact</v>
@@ -45916,7 +45916,7 @@
         <v>0</v>
       </c>
       <c r="F701">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G701" t="str">
         <v>NIP Impact</v>
@@ -45981,7 +45981,7 @@
         <v>0</v>
       </c>
       <c r="F702">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G702" t="str">
         <v>FlyQuest RED</v>
@@ -46046,7 +46046,7 @@
         <v>0</v>
       </c>
       <c r="F703">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G703" t="str">
         <v>FlyQuest RED</v>
@@ -46111,7 +46111,7 @@
         <v>0</v>
       </c>
       <c r="F704">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G704" t="str">
         <v>FlyQuest RED</v>
@@ -46176,7 +46176,7 @@
         <v>0</v>
       </c>
       <c r="F705">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G705" t="str">
         <v>FlyQuest RED</v>
@@ -46241,7 +46241,7 @@
         <v>0</v>
       </c>
       <c r="F706">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G706" t="str">
         <v>FlyQuest RED</v>
@@ -46306,7 +46306,7 @@
         <v>0</v>
       </c>
       <c r="F707">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G707" t="str">
         <v>Heroic Academy</v>
@@ -46371,7 +46371,7 @@
         <v>0</v>
       </c>
       <c r="F708">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G708" t="str">
         <v>Heroic Academy</v>
@@ -46436,7 +46436,7 @@
         <v>0</v>
       </c>
       <c r="F709">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G709" t="str">
         <v>Heroic Academy</v>
@@ -46501,7 +46501,7 @@
         <v>0</v>
       </c>
       <c r="F710">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G710" t="str">
         <v>Heroic Academy</v>
@@ -46566,7 +46566,7 @@
         <v>0</v>
       </c>
       <c r="F711">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G711" t="str">
         <v>Heroic Academy</v>
@@ -46631,7 +46631,7 @@
         <v>0</v>
       </c>
       <c r="F712">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G712" t="str">
         <v>Astralis Talent</v>
@@ -46696,7 +46696,7 @@
         <v>0</v>
       </c>
       <c r="F713">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G713" t="str">
         <v>Astralis Talent</v>
@@ -46761,7 +46761,7 @@
         <v>0</v>
       </c>
       <c r="F714">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G714" t="str">
         <v>Astralis Talent</v>
@@ -46826,7 +46826,7 @@
         <v>0</v>
       </c>
       <c r="F715">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G715" t="str">
         <v>Astralis Talent</v>
@@ -46891,7 +46891,7 @@
         <v>0</v>
       </c>
       <c r="F716">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G716" t="str">
         <v>Astralis Talent</v>
@@ -46956,7 +46956,7 @@
         <v>56</v>
       </c>
       <c r="F717">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G717" t="str">
         <v>BIG Academy</v>
@@ -47021,7 +47021,7 @@
         <v>56</v>
       </c>
       <c r="F718">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G718" t="str">
         <v>BIG Academy</v>
@@ -47086,7 +47086,7 @@
         <v>56</v>
       </c>
       <c r="F719">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G719" t="str">
         <v>BIG Academy</v>
@@ -47151,7 +47151,7 @@
         <v>56</v>
       </c>
       <c r="F720">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G720" t="str">
         <v>BIG Academy</v>
@@ -47216,7 +47216,7 @@
         <v>56</v>
       </c>
       <c r="F721">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G721" t="str">
         <v>BIG Academy</v>
@@ -47281,7 +47281,7 @@
         <v>56</v>
       </c>
       <c r="F722">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G722" t="str">
         <v>ENCE Academy</v>
@@ -47346,7 +47346,7 @@
         <v>56</v>
       </c>
       <c r="F723">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G723" t="str">
         <v>ENCE Academy</v>
@@ -47411,7 +47411,7 @@
         <v>56</v>
       </c>
       <c r="F724">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G724" t="str">
         <v>ENCE Academy</v>
@@ -47476,7 +47476,7 @@
         <v>56</v>
       </c>
       <c r="F725">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G725" t="str">
         <v>ENCE Academy</v>
@@ -47541,7 +47541,7 @@
         <v>56</v>
       </c>
       <c r="F726">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G726" t="str">
         <v>ENCE Academy</v>
@@ -47606,7 +47606,7 @@
         <v>0</v>
       </c>
       <c r="F727">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G727" t="str">
         <v>MOUZ NXT</v>
@@ -47671,7 +47671,7 @@
         <v>0</v>
       </c>
       <c r="F728">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G728" t="str">
         <v>MOUZ NXT</v>
@@ -47736,7 +47736,7 @@
         <v>0</v>
       </c>
       <c r="F729">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G729" t="str">
         <v>MOUZ NXT</v>
@@ -47801,7 +47801,7 @@
         <v>0</v>
       </c>
       <c r="F730">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G730" t="str">
         <v>MOUZ NXT</v>
@@ -47866,7 +47866,7 @@
         <v>0</v>
       </c>
       <c r="F731">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G731" t="str">
         <v>MOUZ NXT</v>
@@ -47931,7 +47931,7 @@
         <v>56</v>
       </c>
       <c r="F732">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G732" t="str">
         <v>Wildcard Academy</v>
@@ -47996,7 +47996,7 @@
         <v>56</v>
       </c>
       <c r="F733">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G733" t="str">
         <v>Wildcard Academy</v>
@@ -48061,7 +48061,7 @@
         <v>56</v>
       </c>
       <c r="F734">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G734" t="str">
         <v>Wildcard Academy</v>
@@ -48126,7 +48126,7 @@
         <v>56</v>
       </c>
       <c r="F735">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G735" t="str">
         <v>Wildcard Academy</v>
@@ -48191,7 +48191,7 @@
         <v>56</v>
       </c>
       <c r="F736">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G736" t="str">
         <v>Wildcard Academy</v>
@@ -48256,7 +48256,7 @@
         <v>0</v>
       </c>
       <c r="F737">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G737" t="str">
         <v>HAVU</v>
@@ -48321,7 +48321,7 @@
         <v>0</v>
       </c>
       <c r="F738">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G738" t="str">
         <v>HAVU</v>
@@ -48386,7 +48386,7 @@
         <v>0</v>
       </c>
       <c r="F739">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G739" t="str">
         <v>HAVU</v>
@@ -48451,7 +48451,7 @@
         <v>0</v>
       </c>
       <c r="F740">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G740" t="str">
         <v>HAVU</v>
@@ -48516,7 +48516,7 @@
         <v>0</v>
       </c>
       <c r="F741">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G741" t="str">
         <v>HAVU</v>
@@ -48581,7 +48581,7 @@
         <v>56</v>
       </c>
       <c r="F742">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G742" t="str">
         <v>SKYFURY</v>
@@ -48646,7 +48646,7 @@
         <v>56</v>
       </c>
       <c r="F743">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G743" t="str">
         <v>SKYFURY</v>
@@ -48711,7 +48711,7 @@
         <v>56</v>
       </c>
       <c r="F744">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G744" t="str">
         <v>SKYFURY</v>
@@ -48776,7 +48776,7 @@
         <v>56</v>
       </c>
       <c r="F745">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G745" t="str">
         <v>SKYFURY</v>
@@ -48841,7 +48841,7 @@
         <v>56</v>
       </c>
       <c r="F746">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G746" t="str">
         <v>SKYFURY</v>
@@ -48906,7 +48906,7 @@
         <v>0</v>
       </c>
       <c r="F747">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G747" t="str">
         <v>Nordix</v>
@@ -48971,7 +48971,7 @@
         <v>0</v>
       </c>
       <c r="F748">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G748" t="str">
         <v>Nordix</v>
@@ -49036,7 +49036,7 @@
         <v>0</v>
       </c>
       <c r="F749">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G749" t="str">
         <v>Nordix</v>
@@ -49101,7 +49101,7 @@
         <v>0</v>
       </c>
       <c r="F750">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G750" t="str">
         <v>Nordix</v>
@@ -49166,7 +49166,7 @@
         <v>0</v>
       </c>
       <c r="F751">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G751" t="str">
         <v>Nordix</v>
@@ -49231,7 +49231,7 @@
         <v>56</v>
       </c>
       <c r="F752">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G752" t="str">
         <v>Shika</v>
@@ -49296,7 +49296,7 @@
         <v>56</v>
       </c>
       <c r="F753">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G753" t="str">
         <v>Shika</v>
@@ -49361,7 +49361,7 @@
         <v>56</v>
       </c>
       <c r="F754">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G754" t="str">
         <v>Shika</v>
@@ -49426,7 +49426,7 @@
         <v>56</v>
       </c>
       <c r="F755">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G755" t="str">
         <v>Shika</v>
@@ -49491,7 +49491,7 @@
         <v>56</v>
       </c>
       <c r="F756">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G756" t="str">
         <v>Shika</v>
@@ -49556,7 +49556,7 @@
         <v>0</v>
       </c>
       <c r="F757">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G757" t="str">
         <v>B8</v>
@@ -49621,7 +49621,7 @@
         <v>0</v>
       </c>
       <c r="F758">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G758" t="str">
         <v>B8</v>
@@ -49686,7 +49686,7 @@
         <v>0</v>
       </c>
       <c r="F759">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G759" t="str">
         <v>B8</v>
@@ -49751,7 +49751,7 @@
         <v>0</v>
       </c>
       <c r="F760">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G760" t="str">
         <v>B8</v>
@@ -49816,7 +49816,7 @@
         <v>0</v>
       </c>
       <c r="F761">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G761" t="str">
         <v>B8</v>
@@ -49881,7 +49881,7 @@
         <v>0</v>
       </c>
       <c r="F762">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G762" t="str">
         <v>MANA</v>
@@ -49946,7 +49946,7 @@
         <v>0</v>
       </c>
       <c r="F763">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G763" t="str">
         <v>MANA</v>
@@ -50011,7 +50011,7 @@
         <v>0</v>
       </c>
       <c r="F764">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G764" t="str">
         <v>MANA</v>
@@ -50076,7 +50076,7 @@
         <v>0</v>
       </c>
       <c r="F765">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G765" t="str">
         <v>MANA</v>
@@ -50141,7 +50141,7 @@
         <v>0</v>
       </c>
       <c r="F766">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G766" t="str">
         <v>MANA</v>
@@ -50206,7 +50206,7 @@
         <v>0</v>
       </c>
       <c r="F767">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G767" t="str">
         <v>MIBR Academy</v>
@@ -50271,7 +50271,7 @@
         <v>0</v>
       </c>
       <c r="F768">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G768" t="str">
         <v>MIBR Academy</v>
@@ -50336,7 +50336,7 @@
         <v>0</v>
       </c>
       <c r="F769">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G769" t="str">
         <v>MIBR Academy</v>
@@ -50401,7 +50401,7 @@
         <v>0</v>
       </c>
       <c r="F770">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G770" t="str">
         <v>MIBR Academy</v>
@@ -50466,7 +50466,7 @@
         <v>0</v>
       </c>
       <c r="F771">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G771" t="str">
         <v>MIBR Academy</v>
@@ -50531,7 +50531,7 @@
         <v>2302.8571428571427</v>
       </c>
       <c r="F772">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G772" t="str">
         <v>AMKAL</v>
@@ -50596,7 +50596,7 @@
         <v>160</v>
       </c>
       <c r="F773">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G773" t="str">
         <v>AMKAL</v>
@@ -50661,7 +50661,7 @@
         <v>160</v>
       </c>
       <c r="F774">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G774" t="str">
         <v>AMKAL</v>
@@ -50726,7 +50726,7 @@
         <v>2302.8571428571427</v>
       </c>
       <c r="F775">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G775" t="str">
         <v>AMKAL</v>
@@ -50791,7 +50791,7 @@
         <v>160</v>
       </c>
       <c r="F776">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G776" t="str">
         <v>AMKAL</v>
@@ -50856,7 +50856,7 @@
         <v>0</v>
       </c>
       <c r="F777">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G777" t="str">
         <v>GhoulsW</v>
@@ -50921,7 +50921,7 @@
         <v>0</v>
       </c>
       <c r="F778">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G778" t="str">
         <v>GhoulsW</v>
@@ -50986,7 +50986,7 @@
         <v>0</v>
       </c>
       <c r="F779">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G779" t="str">
         <v>GhoulsW</v>
@@ -51051,7 +51051,7 @@
         <v>0</v>
       </c>
       <c r="F780">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G780" t="str">
         <v>GhoulsW</v>
@@ -51116,7 +51116,7 @@
         <v>0</v>
       </c>
       <c r="F781">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G781" t="str">
         <v>GhoulsW</v>
@@ -51181,7 +51181,7 @@
         <v>56</v>
       </c>
       <c r="F782">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G782" t="str">
         <v>paiN Academy</v>
@@ -51246,7 +51246,7 @@
         <v>56</v>
       </c>
       <c r="F783">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G783" t="str">
         <v>paiN Academy</v>
@@ -51311,7 +51311,7 @@
         <v>56</v>
       </c>
       <c r="F784">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G784" t="str">
         <v>paiN Academy</v>
@@ -51376,7 +51376,7 @@
         <v>56</v>
       </c>
       <c r="F785">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G785" t="str">
         <v>paiN Academy</v>
@@ -51441,7 +51441,7 @@
         <v>56</v>
       </c>
       <c r="F786">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G786" t="str">
         <v>paiN Academy</v>
@@ -51506,7 +51506,7 @@
         <v>0</v>
       </c>
       <c r="F787">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G787" t="str">
         <v>Aether</v>
@@ -51571,7 +51571,7 @@
         <v>0</v>
       </c>
       <c r="F788">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G788" t="str">
         <v>Aether</v>
@@ -51636,7 +51636,7 @@
         <v>0</v>
       </c>
       <c r="F789">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G789" t="str">
         <v>Aether</v>
@@ -51701,7 +51701,7 @@
         <v>0</v>
       </c>
       <c r="F790">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G790" t="str">
         <v>Aether</v>
@@ -51766,7 +51766,7 @@
         <v>0</v>
       </c>
       <c r="F791">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G791" t="str">
         <v>Aether</v>
@@ -51831,7 +51831,7 @@
         <v>0</v>
       </c>
       <c r="F792">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G792" t="str">
         <v>QMISTRY</v>
@@ -51896,7 +51896,7 @@
         <v>0</v>
       </c>
       <c r="F793">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G793" t="str">
         <v>QMISTRY</v>
@@ -51961,7 +51961,7 @@
         <v>0</v>
       </c>
       <c r="F794">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G794" t="str">
         <v>QMISTRY</v>
@@ -52026,7 +52026,7 @@
         <v>0</v>
       </c>
       <c r="F795">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G795" t="str">
         <v>QMISTRY</v>
@@ -52091,7 +52091,7 @@
         <v>0</v>
       </c>
       <c r="F796">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G796" t="str">
         <v>QMISTRY</v>
@@ -52156,7 +52156,7 @@
         <v>0</v>
       </c>
       <c r="F797">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G797" t="str">
         <v>Tsunami</v>
@@ -52221,7 +52221,7 @@
         <v>0</v>
       </c>
       <c r="F798">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G798" t="str">
         <v>Tsunami</v>
@@ -52286,7 +52286,7 @@
         <v>0</v>
       </c>
       <c r="F799">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G799" t="str">
         <v>Tsunami</v>
@@ -52351,7 +52351,7 @@
         <v>0</v>
       </c>
       <c r="F800">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G800" t="str">
         <v>Tsunami</v>
@@ -52416,7 +52416,7 @@
         <v>0</v>
       </c>
       <c r="F801">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G801" t="str">
         <v>Tsunami</v>
@@ -52481,7 +52481,7 @@
         <v>0</v>
       </c>
       <c r="F802">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G802" t="str">
         <v>NOVAQ</v>
@@ -52546,7 +52546,7 @@
         <v>0</v>
       </c>
       <c r="F803">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G803" t="str">
         <v>NOVAQ</v>
@@ -52611,7 +52611,7 @@
         <v>0</v>
       </c>
       <c r="F804">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G804" t="str">
         <v>NOVAQ</v>
@@ -52676,7 +52676,7 @@
         <v>0</v>
       </c>
       <c r="F805">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G805" t="str">
         <v>NOVAQ</v>
@@ -52741,7 +52741,7 @@
         <v>0</v>
       </c>
       <c r="F806">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G806" t="str">
         <v>NOVAQ</v>
@@ -52806,7 +52806,7 @@
         <v>0</v>
       </c>
       <c r="F807">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G807" t="str">
         <v>Hesta</v>
@@ -52871,7 +52871,7 @@
         <v>0</v>
       </c>
       <c r="F808">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G808" t="str">
         <v>Hesta</v>
@@ -52936,7 +52936,7 @@
         <v>0</v>
       </c>
       <c r="F809">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G809" t="str">
         <v>Hesta</v>
@@ -53001,7 +53001,7 @@
         <v>0</v>
       </c>
       <c r="F810">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G810" t="str">
         <v>Hesta</v>
@@ -53066,7 +53066,7 @@
         <v>0</v>
       </c>
       <c r="F811">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G811" t="str">
         <v>Hesta</v>
@@ -53131,7 +53131,7 @@
         <v>2302.8571428571427</v>
       </c>
       <c r="F812">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G812" t="str">
         <v>kONO</v>
@@ -53196,7 +53196,7 @@
         <v>3731.428571428571</v>
       </c>
       <c r="F813">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G813" t="str">
         <v>kONO</v>
@@ -53261,7 +53261,7 @@
         <v>5160</v>
       </c>
       <c r="F814">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G814" t="str">
         <v>kONO</v>
@@ -53326,7 +53326,7 @@
         <v>160</v>
       </c>
       <c r="F815">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G815" t="str">
         <v>kONO</v>
@@ -53391,7 +53391,7 @@
         <v>160</v>
       </c>
       <c r="F816">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G816" t="str">
         <v>kONO</v>
@@ -53456,7 +53456,7 @@
         <v>56</v>
       </c>
       <c r="F817">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G817" t="str">
         <v>GATERON</v>
@@ -53521,7 +53521,7 @@
         <v>56</v>
       </c>
       <c r="F818">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G818" t="str">
         <v>GATERON</v>
@@ -53586,7 +53586,7 @@
         <v>56</v>
       </c>
       <c r="F819">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G819" t="str">
         <v>GATERON</v>
@@ -53651,7 +53651,7 @@
         <v>56</v>
       </c>
       <c r="F820">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G820" t="str">
         <v>GATERON</v>
@@ -53716,7 +53716,7 @@
         <v>56</v>
       </c>
       <c r="F821">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G821" t="str">
         <v>GATERON</v>
@@ -53834,7 +53834,7 @@
         <v>Perfecto</v>
       </c>
       <c r="B823" t="str">
-        <v>Bench</v>
+        <v>Starter</v>
       </c>
       <c r="C823" t="str">
         <v>anchor</v>
@@ -53846,7 +53846,7 @@
         <v>0</v>
       </c>
       <c r="F823">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G823" t="str">
         <v>BC.Game</v>
@@ -54614,7 +54614,7 @@
         <v>kl1m</v>
       </c>
       <c r="B835" t="str">
-        <v>Bench</v>
+        <v>Starter</v>
       </c>
       <c r="C835" t="str">
         <v>entry fragger</v>
@@ -54626,7 +54626,7 @@
         <v>0</v>
       </c>
       <c r="F835">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G835" t="str">
         <v>Envy</v>
@@ -55146,7 +55146,7 @@
         <v>0</v>
       </c>
       <c r="F843">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G843" t="str">
         <v>Kappa Bar</v>
@@ -55536,7 +55536,7 @@
         <v>56</v>
       </c>
       <c r="F849">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G849" t="str">
         <v>Mythic</v>
@@ -56511,7 +56511,7 @@
         <v>2382.8571428571427</v>
       </c>
       <c r="F864">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G864" t="str">
         <v>Lux Tenebris</v>
@@ -56771,7 +56771,7 @@
         <v>2382.8571428571427</v>
       </c>
       <c r="F868">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G868" t="str">
         <v>Lux Tenebris</v>
@@ -56901,7 +56901,7 @@
         <v>240</v>
       </c>
       <c r="F870">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G870" t="str">
         <v>Lux Tenebris</v>
